--- a/outputs/model.xlsx
+++ b/outputs/model.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C34"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>23 October 2026</t>
+          <t>24 October 2026</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C11" s="6">
-        <f>'DCF'!D49</f>
+        <f>'DCF'!D50</f>
         <v/>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C12" s="6">
-        <f>'DCF'!E49</f>
+        <f>'DCF'!E50</f>
         <v/>
       </c>
     </row>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="C15" s="6">
-        <f>'LBO'!D14</f>
+        <f>'LBO'!D15</f>
         <v/>
       </c>
     </row>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C16" s="9">
-        <f>'LBO'!D39</f>
+        <f>'LBO'!D40</f>
         <v/>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>'LBO'!D100</f>
+        <f>'LBO'!D102</f>
         <v/>
       </c>
     </row>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>'LBO'!D101</f>
+        <f>'LBO'!D103</f>
         <v/>
       </c>
     </row>
@@ -995,21 +995,28 @@
     <row r="32">
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>Funded debt is refinanced (held flat) in the standalone projection.</t>
+          <t>Term debt is held flat in the projection; any cash shortfall is drawn on a revolver.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Offshore cash is valued net of the repatriation tax implied by the 10-K.</t>
+          <t>Dividends and buybacks are paid from positive earnings, limited to available cash.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Apple is far beyond any realised LBO size; the LBO is a hypothetical stress test.</t>
+          <t>Offshore cash (where disclosed) is valued net of the implied repatriation tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>The LBO is an illustrative take-private analysis, not a financing commitment.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1639,7 @@
     <row r="2">
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Every check must be zero (within $0.5M). Flag 1 = error.</t>
+          <t>Every check must be zero, within $1M (the filing's own rounding). Flag 1 = error.</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1678,11 @@
         </is>
       </c>
       <c r="C6" s="53">
-        <f>'IS'!D36</f>
+        <f>'IS'!D38</f>
         <v/>
       </c>
       <c r="D6" s="91">
-        <f>IF(ABS(C6)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C6)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1686,11 +1693,11 @@
         </is>
       </c>
       <c r="C7" s="53">
-        <f>'IS'!E36</f>
+        <f>'IS'!E38</f>
         <v/>
       </c>
       <c r="D7" s="91">
-        <f>IF(ABS(C7)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C7)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1701,11 +1708,11 @@
         </is>
       </c>
       <c r="C8" s="53">
-        <f>'IS'!F36</f>
+        <f>'IS'!F38</f>
         <v/>
       </c>
       <c r="D8" s="91">
-        <f>IF(ABS(C8)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C8)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1716,11 +1723,11 @@
         </is>
       </c>
       <c r="C9" s="53">
-        <f>'IS'!D45</f>
+        <f>'IS'!D47</f>
         <v/>
       </c>
       <c r="D9" s="91">
-        <f>IF(ABS(C9)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C9)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1731,11 +1738,11 @@
         </is>
       </c>
       <c r="C10" s="53">
-        <f>'IS'!E45</f>
+        <f>'IS'!E47</f>
         <v/>
       </c>
       <c r="D10" s="91">
-        <f>IF(ABS(C10)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C10)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1746,11 +1753,11 @@
         </is>
       </c>
       <c r="C11" s="53">
-        <f>'IS'!F45</f>
+        <f>'IS'!F47</f>
         <v/>
       </c>
       <c r="D11" s="91">
-        <f>IF(ABS(C11)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C11)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1761,11 +1768,11 @@
         </is>
       </c>
       <c r="C12" s="53">
-        <f>'BS'!E40</f>
+        <f>'BS'!E43</f>
         <v/>
       </c>
       <c r="D12" s="91">
-        <f>IF(ABS(C12)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C12)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1776,11 +1783,11 @@
         </is>
       </c>
       <c r="C13" s="53">
-        <f>'BS'!F40</f>
+        <f>'BS'!F43</f>
         <v/>
       </c>
       <c r="D13" s="91">
-        <f>IF(ABS(C13)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C13)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1791,11 +1798,11 @@
         </is>
       </c>
       <c r="C14" s="53">
-        <f>'BS'!G40</f>
+        <f>'BS'!G43</f>
         <v/>
       </c>
       <c r="D14" s="91">
-        <f>IF(ABS(C14)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C14)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1806,11 +1813,11 @@
         </is>
       </c>
       <c r="C15" s="53">
-        <f>'BS'!H40</f>
+        <f>'BS'!H43</f>
         <v/>
       </c>
       <c r="D15" s="91">
-        <f>IF(ABS(C15)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C15)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1821,11 +1828,11 @@
         </is>
       </c>
       <c r="C16" s="53">
-        <f>'BS'!I40</f>
+        <f>'BS'!I43</f>
         <v/>
       </c>
       <c r="D16" s="91">
-        <f>IF(ABS(C16)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C16)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1836,11 +1843,11 @@
         </is>
       </c>
       <c r="C17" s="53">
-        <f>'BS'!J40</f>
+        <f>'BS'!J43</f>
         <v/>
       </c>
       <c r="D17" s="91">
-        <f>IF(ABS(C17)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C17)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1851,116 +1858,116 @@
         </is>
       </c>
       <c r="C18" s="53">
-        <f>'BS'!K40</f>
+        <f>'BS'!K43</f>
         <v/>
       </c>
       <c r="D18" s="91">
-        <f>IF(ABS(C18)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C18)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2014</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2014</t>
         </is>
       </c>
       <c r="C19" s="53">
-        <f>'CFS'!E47</f>
+        <f>'CFS'!E49</f>
         <v/>
       </c>
       <c r="D19" s="91">
-        <f>IF(ABS(C19)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C19)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2015</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2015</t>
         </is>
       </c>
       <c r="C20" s="53">
-        <f>'CFS'!F47</f>
+        <f>'CFS'!F49</f>
         <v/>
       </c>
       <c r="D20" s="91">
-        <f>IF(ABS(C20)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C20)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2016</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2016</t>
         </is>
       </c>
       <c r="C21" s="53">
-        <f>'CFS'!G47</f>
+        <f>'CFS'!G49</f>
         <v/>
       </c>
       <c r="D21" s="91">
-        <f>IF(ABS(C21)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C21)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2017</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2017</t>
         </is>
       </c>
       <c r="C22" s="53">
-        <f>'CFS'!H47</f>
+        <f>'CFS'!H49</f>
         <v/>
       </c>
       <c r="D22" s="91">
-        <f>IF(ABS(C22)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C22)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2018</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2018</t>
         </is>
       </c>
       <c r="C23" s="53">
-        <f>'CFS'!I47</f>
+        <f>'CFS'!I49</f>
         <v/>
       </c>
       <c r="D23" s="91">
-        <f>IF(ABS(C23)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C23)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2019</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2019</t>
         </is>
       </c>
       <c r="C24" s="53">
-        <f>'CFS'!J47</f>
+        <f>'CFS'!J49</f>
         <v/>
       </c>
       <c r="D24" s="91">
-        <f>IF(ABS(C24)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C24)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>CFS: Check: ending cash - balance sheet cash FY2020</t>
+          <t>CFS: Check: ending cash ex. restricted - balance sheet cash FY2020</t>
         </is>
       </c>
       <c r="C25" s="53">
-        <f>'CFS'!K47</f>
+        <f>'CFS'!K49</f>
         <v/>
       </c>
       <c r="D25" s="91">
-        <f>IF(ABS(C25)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C25)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1971,11 +1978,11 @@
         </is>
       </c>
       <c r="C26" s="53">
-        <f>'CFS'!D48</f>
+        <f>'CFS'!D50</f>
         <v/>
       </c>
       <c r="D26" s="91">
-        <f>IF(ABS(C26)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C26)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -1986,11 +1993,11 @@
         </is>
       </c>
       <c r="C27" s="53">
-        <f>'CFS'!E48</f>
+        <f>'CFS'!E50</f>
         <v/>
       </c>
       <c r="D27" s="91">
-        <f>IF(ABS(C27)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C27)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -2001,11 +2008,11 @@
         </is>
       </c>
       <c r="C28" s="53">
-        <f>'CFS'!F48</f>
+        <f>'CFS'!F50</f>
         <v/>
       </c>
       <c r="D28" s="91">
-        <f>IF(ABS(C28)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C28)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -2020,7 +2027,7 @@
         <v/>
       </c>
       <c r="D29" s="91">
-        <f>IF(ABS(C29)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C29)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -2035,7 +2042,7 @@
         <v/>
       </c>
       <c r="D30" s="91">
-        <f>IF(ABS(C30)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C30)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -2046,11 +2053,11 @@
         </is>
       </c>
       <c r="C31" s="53">
-        <f>'LBO'!D41</f>
+        <f>'LBO'!D42</f>
         <v/>
       </c>
       <c r="D31" s="91">
-        <f>IF(ABS(C31)&lt;0.5,0,1)</f>
+        <f>IF(ABS(C31)&lt;=1.000001,0,1)</f>
         <v/>
       </c>
     </row>
@@ -2065,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K72"/>
+  <dimension ref="B1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2259,7 +2266,7 @@
         </is>
       </c>
       <c r="D16" s="31">
-        <f>D26/D25</f>
+        <f>IF(D25=0,0,D26/D25)</f>
         <v/>
       </c>
     </row>
@@ -2541,152 +2548,151 @@
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>D&amp;A, % of sales</t>
+          <t>Other operating expenses, % of sales</t>
         </is>
       </c>
       <c r="D34" s="36">
-        <f>'IS'!D16/'IS'!D7</f>
+        <f>'IS'!D13/'IS'!D7</f>
         <v/>
       </c>
       <c r="E34" s="36">
-        <f>'IS'!E16/'IS'!E7</f>
+        <f>'IS'!E13/'IS'!E7</f>
         <v/>
       </c>
       <c r="F34" s="36">
-        <f>'IS'!F16/'IS'!F7</f>
+        <f>'IS'!F13/'IS'!F7</f>
         <v/>
       </c>
       <c r="G34" s="28" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="J34" s="28" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>Capex, % of sales</t>
+          <t>D&amp;A, % of sales</t>
         </is>
       </c>
       <c r="D35" s="36">
-        <f>-'CFS'!D28/'IS'!D7</f>
+        <f>'IS'!D17/'IS'!D7</f>
         <v/>
       </c>
       <c r="E35" s="36">
-        <f>-'CFS'!E28/'IS'!E7</f>
+        <f>'IS'!E17/'IS'!E7</f>
         <v/>
       </c>
       <c r="F35" s="36">
-        <f>-'CFS'!F28/'IS'!F7</f>
+        <f>'IS'!F17/'IS'!F7</f>
         <v/>
       </c>
       <c r="G35" s="28" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="H35" s="28" t="n">
-        <v>0.055</v>
+        <v>0.048</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="J35" s="28" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="K35" s="28" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>Tax rate</t>
+          <t>Capex, % of sales</t>
         </is>
       </c>
       <c r="D36" s="36">
-        <f>'IS'!D23/'IS'!D22</f>
+        <f>-'CFS'!D28/'IS'!D7</f>
         <v/>
       </c>
       <c r="E36" s="36">
-        <f>'IS'!E23/'IS'!E22</f>
+        <f>-'CFS'!E28/'IS'!E7</f>
         <v/>
       </c>
       <c r="F36" s="36">
-        <f>'IS'!F23/'IS'!F22</f>
+        <f>-'CFS'!F28/'IS'!F7</f>
         <v/>
       </c>
       <c r="G36" s="28" t="n">
-        <v>0.264</v>
+        <v>0.06</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>0.264</v>
+        <v>0.055</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>0.264</v>
+        <v>0.05</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>0.264</v>
+        <v>0.05</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>0.264</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Receivable days</t>
-        </is>
-      </c>
-      <c r="E37" s="37">
-        <f>'BS'!E9/'IS'!E7*$D$17</f>
-        <v/>
-      </c>
-      <c r="F37" s="37">
-        <f>'BS'!F9/'IS'!F7*$D$17</f>
-        <v/>
-      </c>
-      <c r="G37" s="38">
-        <f>$F$37</f>
-        <v/>
-      </c>
-      <c r="H37" s="38">
-        <f>$F$37</f>
-        <v/>
-      </c>
-      <c r="I37" s="38">
-        <f>$F$37</f>
-        <v/>
-      </c>
-      <c r="J37" s="38">
-        <f>$F$37</f>
-        <v/>
-      </c>
-      <c r="K37" s="38">
-        <f>$F$37</f>
-        <v/>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="D37" s="36">
+        <f>'IS'!D24/'IS'!D23</f>
+        <v/>
+      </c>
+      <c r="E37" s="36">
+        <f>'IS'!E24/'IS'!E23</f>
+        <v/>
+      </c>
+      <c r="F37" s="36">
+        <f>'IS'!F24/'IS'!F23</f>
+        <v/>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="J37" s="28" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="K37" s="28" t="n">
+        <v>0.264</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>Inventory days</t>
+          <t>Receivable days</t>
         </is>
       </c>
       <c r="E38" s="37">
-        <f>'BS'!E10/'IS'!E8*$D$17</f>
+        <f>'BS'!E9/'IS'!E7*$D$17</f>
         <v/>
       </c>
       <c r="F38" s="37">
-        <f>'BS'!F10/'IS'!F8*$D$17</f>
+        <f>'BS'!F9/'IS'!F7*$D$17</f>
         <v/>
       </c>
       <c r="G38" s="38">
@@ -2713,15 +2719,15 @@
     <row r="39">
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Payable days</t>
+          <t>Inventory days</t>
         </is>
       </c>
       <c r="E39" s="37">
-        <f>'BS'!E23/'IS'!E8*$D$17</f>
+        <f>'BS'!E10/'IS'!E8*$D$17</f>
         <v/>
       </c>
       <c r="F39" s="37">
-        <f>'BS'!F23/'IS'!F8*$D$17</f>
+        <f>'BS'!F10/'IS'!F8*$D$17</f>
         <v/>
       </c>
       <c r="G39" s="38">
@@ -2748,34 +2754,34 @@
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>Vendor receivables % sales</t>
-        </is>
-      </c>
-      <c r="E40" s="36">
-        <f>'BS'!E12/'IS'!E7</f>
-        <v/>
-      </c>
-      <c r="F40" s="36">
-        <f>'BS'!F12/'IS'!F7</f>
-        <v/>
-      </c>
-      <c r="G40" s="31">
+          <t>Payable days</t>
+        </is>
+      </c>
+      <c r="E40" s="37">
+        <f>'BS'!E23/'IS'!E8*$D$17</f>
+        <v/>
+      </c>
+      <c r="F40" s="37">
+        <f>'BS'!F23/'IS'!F8*$D$17</f>
+        <v/>
+      </c>
+      <c r="G40" s="38">
         <f>$F$40</f>
         <v/>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="38">
         <f>$F$40</f>
         <v/>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="38">
         <f>$F$40</f>
         <v/>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="38">
         <f>$F$40</f>
         <v/>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="38">
         <f>$F$40</f>
         <v/>
       </c>
@@ -2783,15 +2789,15 @@
     <row r="41">
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Other current assets % sales</t>
+          <t>Vendor receivables % sales</t>
         </is>
       </c>
       <c r="E41" s="36">
-        <f>'BS'!E13/'IS'!E7</f>
+        <f>'BS'!E12/'IS'!E7</f>
         <v/>
       </c>
       <c r="F41" s="36">
-        <f>'BS'!F13/'IS'!F7</f>
+        <f>'BS'!F12/'IS'!F7</f>
         <v/>
       </c>
       <c r="G41" s="31">
@@ -2818,15 +2824,15 @@
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>Accrued expenses % sales</t>
+          <t>Other current assets % sales</t>
         </is>
       </c>
       <c r="E42" s="36">
-        <f>'BS'!E24/'IS'!E7</f>
+        <f>'BS'!E13/'IS'!E7</f>
         <v/>
       </c>
       <c r="F42" s="36">
-        <f>'BS'!F24/'IS'!F7</f>
+        <f>'BS'!F13/'IS'!F7</f>
         <v/>
       </c>
       <c r="G42" s="31">
@@ -2853,15 +2859,15 @@
     <row r="43">
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>Deferred revenue % sales</t>
+          <t>Accrued expenses % sales</t>
         </is>
       </c>
       <c r="E43" s="36">
-        <f>'BS'!E25/'IS'!E7</f>
+        <f>'BS'!E24/'IS'!E7</f>
         <v/>
       </c>
       <c r="F43" s="36">
-        <f>'BS'!F25/'IS'!F7</f>
+        <f>'BS'!F24/'IS'!F7</f>
         <v/>
       </c>
       <c r="G43" s="31">
@@ -2888,155 +2894,180 @@
     <row r="44">
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>Interest income yield on cash &amp; securities</t>
-        </is>
-      </c>
-      <c r="G44" s="39">
-        <f>$D$27</f>
-        <v/>
-      </c>
-      <c r="H44" s="39">
-        <f>$D$27</f>
-        <v/>
-      </c>
-      <c r="I44" s="39">
-        <f>$D$27</f>
-        <v/>
-      </c>
-      <c r="J44" s="39">
-        <f>$D$27</f>
-        <v/>
-      </c>
-      <c r="K44" s="39">
-        <f>$D$27</f>
+          <t>Deferred revenue % sales</t>
+        </is>
+      </c>
+      <c r="E44" s="36">
+        <f>'BS'!E25/'IS'!E7</f>
+        <v/>
+      </c>
+      <c r="F44" s="36">
+        <f>'BS'!F25/'IS'!F7</f>
+        <v/>
+      </c>
+      <c r="G44" s="31">
+        <f>$F$44</f>
+        <v/>
+      </c>
+      <c r="H44" s="31">
+        <f>$F$44</f>
+        <v/>
+      </c>
+      <c r="I44" s="31">
+        <f>$F$44</f>
+        <v/>
+      </c>
+      <c r="J44" s="31">
+        <f>$F$44</f>
+        <v/>
+      </c>
+      <c r="K44" s="31">
+        <f>$F$44</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="G45" s="40">
-        <f>'Debt'!$D$48</f>
-        <v/>
-      </c>
-      <c r="H45" s="40">
-        <f>'Debt'!$D$48</f>
-        <v/>
-      </c>
-      <c r="I45" s="40">
-        <f>'Debt'!$D$48</f>
-        <v/>
-      </c>
-      <c r="J45" s="40">
-        <f>'Debt'!$D$48</f>
-        <v/>
-      </c>
-      <c r="K45" s="40">
-        <f>'Debt'!$D$48</f>
+          <t>Interest income yield on cash &amp; securities</t>
+        </is>
+      </c>
+      <c r="G45" s="39">
+        <f>$D$27</f>
+        <v/>
+      </c>
+      <c r="H45" s="39">
+        <f>$D$27</f>
+        <v/>
+      </c>
+      <c r="I45" s="39">
+        <f>$D$27</f>
+        <v/>
+      </c>
+      <c r="J45" s="39">
+        <f>$D$27</f>
+        <v/>
+      </c>
+      <c r="K45" s="39">
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>Dividends, % of net income</t>
-        </is>
-      </c>
-      <c r="D46" s="36">
-        <f>-'CFS'!D37/'IS'!D24</f>
-        <v/>
-      </c>
-      <c r="E46" s="36">
-        <f>-'CFS'!E37/'IS'!E24</f>
-        <v/>
-      </c>
-      <c r="F46" s="36">
-        <f>-'CFS'!F37/'IS'!F24</f>
-        <v/>
-      </c>
-      <c r="G46" s="28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J46" s="28" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="K46" s="28" t="n">
-        <v>0.22</v>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="G46" s="40">
+        <f>'Debt'!$D$48</f>
+        <v/>
+      </c>
+      <c r="H46" s="40">
+        <f>'Debt'!$D$48</f>
+        <v/>
+      </c>
+      <c r="I46" s="40">
+        <f>'Debt'!$D$48</f>
+        <v/>
+      </c>
+      <c r="J46" s="40">
+        <f>'Debt'!$D$48</f>
+        <v/>
+      </c>
+      <c r="K46" s="40">
+        <f>'Debt'!$D$48</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="24" t="inlineStr">
         <is>
+          <t>Dividends, % of net income</t>
+        </is>
+      </c>
+      <c r="D47" s="36">
+        <f>-'CFS'!D37/'IS'!D26</f>
+        <v/>
+      </c>
+      <c r="E47" s="36">
+        <f>-'CFS'!E37/'IS'!E26</f>
+        <v/>
+      </c>
+      <c r="F47" s="36">
+        <f>-'CFS'!F37/'IS'!F26</f>
+        <v/>
+      </c>
+      <c r="G47" s="28" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J47" s="28" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="24" t="inlineStr">
+        <is>
           <t>Share repurchases, % of net income</t>
         </is>
       </c>
-      <c r="D47" s="36">
-        <f>-'CFS'!D38/'IS'!D24</f>
-        <v/>
-      </c>
-      <c r="E47" s="36">
-        <f>-'CFS'!E38/'IS'!E24</f>
-        <v/>
-      </c>
-      <c r="F47" s="36">
-        <f>-'CFS'!F38/'IS'!F24</f>
-        <v/>
-      </c>
-      <c r="G47" s="28" t="n">
+      <c r="D48" s="36">
+        <f>-'CFS'!D38/'IS'!D26</f>
+        <v/>
+      </c>
+      <c r="E48" s="36">
+        <f>-'CFS'!E38/'IS'!E26</f>
+        <v/>
+      </c>
+      <c r="F48" s="36">
+        <f>-'CFS'!F38/'IS'!F26</f>
+        <v/>
+      </c>
+      <c r="G48" s="28" t="n">
         <v>0.65</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H48" s="28" t="n">
         <v>0.65</v>
       </c>
-      <c r="I47" s="28" t="n">
+      <c r="I48" s="28" t="n">
         <v>0.65</v>
       </c>
-      <c r="J47" s="28" t="n">
+      <c r="J48" s="28" t="n">
         <v>0.65</v>
       </c>
-      <c r="K47" s="28" t="n">
+      <c r="K48" s="28" t="n">
         <v>0.65</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Transaction assumptions (LBO)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="23" t="n"/>
-      <c r="G49" s="23" t="n"/>
-      <c r="H49" s="23" t="n"/>
-      <c r="I49" s="23" t="n"/>
-      <c r="J49" s="23" t="n"/>
-      <c r="K49" s="23" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Entry EV / LTM EBITDA</t>
-        </is>
-      </c>
-      <c r="D50" s="29" t="n">
-        <v>8</v>
-      </c>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="23" t="n"/>
+      <c r="J50" s="23" t="n"/>
+      <c r="K50" s="23" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>Exit EV / EBITDA</t>
+          <t>Entry EV / LTM EBITDA</t>
         </is>
       </c>
       <c r="D51" s="29" t="n">
@@ -3046,202 +3077,212 @@
     <row r="52">
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>Holding period (years)</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>5</v>
+          <t>Exit EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Total debt, % of entry EV</t>
-        </is>
-      </c>
-      <c r="D53" s="28" t="n">
-        <v>0.5</v>
+          <t>Holding period (years)</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>Excess cash flow sweep</t>
+          <t>Total debt, % of entry EV</t>
         </is>
       </c>
       <c r="D54" s="28" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>Minimum operating cash</t>
-        </is>
-      </c>
-      <c r="D55" s="35" t="n">
-        <v>10000</v>
+          <t>Excess cash flow sweep</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>Advisory &amp; transaction fees, % of EV</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="n">
-        <v>0.01</v>
+          <t>Minimum operating cash</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Financing fees, % of debt</t>
+          <t>Advisory &amp; transaction fees, % of EV</t>
         </is>
       </c>
       <c r="D57" s="26" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>Offshore cash repatriated at close</t>
-        </is>
-      </c>
-      <c r="D58" s="28" t="n">
-        <v>0</v>
+          <t>Financing fees, % of debt</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Covenant: maximum Total debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="n">
-        <v>5</v>
+          <t>Offshore cash repatriated at close</t>
+        </is>
+      </c>
+      <c r="D59" s="28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="24" t="inlineStr">
         <is>
+          <t>Covenant: maximum Total debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="24" t="inlineStr">
+        <is>
           <t>Covenant: minimum EBITDA / Interest</t>
         </is>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D61" s="29" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="23" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="23" t="inlineStr">
         <is>
           <t>Tranche 1: Senior Term Loan B (senior secured)</t>
         </is>
       </c>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="23" t="n"/>
-      <c r="F62" s="23" t="n"/>
-      <c r="G62" s="23" t="n"/>
-      <c r="H62" s="23" t="n"/>
-      <c r="I62" s="23" t="n"/>
-      <c r="J62" s="23" t="n"/>
-      <c r="K62" s="23" t="n"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>Share of total debt</t>
-        </is>
-      </c>
-      <c r="D63" s="28" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="C63" s="23" t="n"/>
+      <c r="D63" s="23" t="n"/>
+      <c r="E63" s="23" t="n"/>
+      <c r="F63" s="23" t="n"/>
+      <c r="G63" s="23" t="n"/>
+      <c r="H63" s="23" t="n"/>
+      <c r="I63" s="23" t="n"/>
+      <c r="J63" s="23" t="n"/>
+      <c r="K63" s="23" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>Cash interest rate</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="n">
-        <v>0.055</v>
+          <t>Share of total debt</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>Mandatory amortization, % of original</t>
-        </is>
-      </c>
-      <c r="D65" s="28" t="n">
-        <v>0.01</v>
+          <t>Cash interest rate</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="24" t="inlineStr">
         <is>
+          <t>Mandatory amortization, % of original</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="24" t="inlineStr">
+        <is>
           <t>Prepayable from sweep (1 = yes)</t>
         </is>
       </c>
-      <c r="D66" s="30" t="n">
+      <c r="D67" s="30" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="23" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="23" t="inlineStr">
         <is>
           <t>Tranche 2: Senior Subordinated Notes (subordinated)</t>
         </is>
       </c>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="23" t="n"/>
-      <c r="E68" s="23" t="n"/>
-      <c r="F68" s="23" t="n"/>
-      <c r="G68" s="23" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="23" t="n"/>
-      <c r="K68" s="23" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>Share of total debt</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="C69" s="23" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+      <c r="F69" s="23" t="n"/>
+      <c r="G69" s="23" t="n"/>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="23" t="n"/>
+      <c r="J69" s="23" t="n"/>
+      <c r="K69" s="23" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>Cash interest rate</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="n">
-        <v>0.08</v>
+          <t>Share of total debt</t>
+        </is>
+      </c>
+      <c r="D70" s="28" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>Mandatory amortization, % of original</t>
-        </is>
-      </c>
-      <c r="D71" s="28" t="n">
-        <v>0</v>
+          <t>Cash interest rate</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="24" t="inlineStr">
         <is>
+          <t>Mandatory amortization, % of original</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="24" t="inlineStr">
+        <is>
           <t>Prepayable from sweep (1 = yes)</t>
         </is>
       </c>
-      <c r="D72" s="30" t="n">
+      <c r="D73" s="30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3261,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K45"/>
+  <dimension ref="B1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3581,788 +3622,840 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="41" t="inlineStr">
-        <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D13" s="46">
-        <f>SUM(D11:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="46">
-        <f>SUM(E11:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="46">
-        <f>SUM(F11:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="46">
-        <f>SUM(G11:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="46">
-        <f>SUM(H11:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="46">
-        <f>SUM(I11:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="46">
-        <f>SUM(J11:J12)</f>
-        <v/>
-      </c>
-      <c r="K13" s="46">
-        <f>SUM(K11:K12)</f>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="45">
+        <f>G7*'Inputs'!G34</f>
+        <v/>
+      </c>
+      <c r="H13" s="45">
+        <f>H7*'Inputs'!H34</f>
+        <v/>
+      </c>
+      <c r="I13" s="45">
+        <f>I7*'Inputs'!I34</f>
+        <v/>
+      </c>
+      <c r="J13" s="45">
+        <f>J7*'Inputs'!J34</f>
+        <v/>
+      </c>
+      <c r="K13" s="45">
+        <f>K7*'Inputs'!K34</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="41" t="inlineStr">
         <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D14" s="46">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="46">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="46">
+        <f>SUM(F11:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="46">
+        <f>SUM(G11:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="46">
+        <f>SUM(H11:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="46">
+        <f>SUM(I11:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="46">
+        <f>SUM(J11:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>SUM(K11:K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
           <t>Operating income (EBIT)</t>
         </is>
       </c>
-      <c r="D14" s="46">
-        <f>D9-D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="46">
-        <f>E9-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="46">
-        <f>F9-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="46">
-        <f>G9-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="46">
-        <f>H9-H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="46">
-        <f>I9-I13</f>
-        <v/>
-      </c>
-      <c r="J14" s="46">
-        <f>J9-J13</f>
-        <v/>
-      </c>
-      <c r="K14" s="46">
-        <f>K9-K13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin %</t>
-        </is>
-      </c>
-      <c r="D15" s="48">
-        <f>D14/D7</f>
-        <v/>
-      </c>
-      <c r="E15" s="48">
-        <f>E14/E7</f>
-        <v/>
-      </c>
-      <c r="F15" s="48">
-        <f>F14/F7</f>
-        <v/>
-      </c>
-      <c r="G15" s="48">
-        <f>G14/G7</f>
-        <v/>
-      </c>
-      <c r="H15" s="48">
-        <f>H14/H7</f>
-        <v/>
-      </c>
-      <c r="I15" s="48">
-        <f>I14/I7</f>
-        <v/>
-      </c>
-      <c r="J15" s="48">
-        <f>J14/J7</f>
-        <v/>
-      </c>
-      <c r="K15" s="48">
-        <f>K14/K7</f>
+      <c r="D15" s="46">
+        <f>D9-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="46">
+        <f>E9-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="46">
+        <f>F9-F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="46">
+        <f>G9-G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="46">
+        <f>H9-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="46">
+        <f>I9-I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="46">
+        <f>J9-J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="46">
+        <f>K9-K14</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="47" t="inlineStr">
         <is>
+          <t xml:space="preserve">  EBIT margin %</t>
+        </is>
+      </c>
+      <c r="D16" s="48">
+        <f>D15/D7</f>
+        <v/>
+      </c>
+      <c r="E16" s="48">
+        <f>E15/E7</f>
+        <v/>
+      </c>
+      <c r="F16" s="48">
+        <f>F15/F7</f>
+        <v/>
+      </c>
+      <c r="G16" s="48">
+        <f>G15/G7</f>
+        <v/>
+      </c>
+      <c r="H16" s="48">
+        <f>H15/H7</f>
+        <v/>
+      </c>
+      <c r="I16" s="48">
+        <f>I15/I7</f>
+        <v/>
+      </c>
+      <c r="J16" s="48">
+        <f>J15/J7</f>
+        <v/>
+      </c>
+      <c r="K16" s="48">
+        <f>K15/K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="47" t="inlineStr">
+        <is>
           <t>Depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D16" s="49">
+      <c r="D17" s="49">
         <f>'CFS'!D10</f>
         <v/>
       </c>
-      <c r="E16" s="49">
+      <c r="E17" s="49">
         <f>'CFS'!E10</f>
         <v/>
       </c>
-      <c r="F16" s="49">
+      <c r="F17" s="49">
         <f>'CFS'!F10</f>
         <v/>
       </c>
-      <c r="G16" s="49">
-        <f>G7*'Inputs'!G34</f>
-        <v/>
-      </c>
-      <c r="H16" s="49">
-        <f>H7*'Inputs'!H34</f>
-        <v/>
-      </c>
-      <c r="I16" s="49">
-        <f>I7*'Inputs'!I34</f>
-        <v/>
-      </c>
-      <c r="J16" s="49">
-        <f>J7*'Inputs'!J34</f>
-        <v/>
-      </c>
-      <c r="K16" s="49">
-        <f>K7*'Inputs'!K34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="41" t="inlineStr">
+      <c r="G17" s="49">
+        <f>G7*'Inputs'!G35</f>
+        <v/>
+      </c>
+      <c r="H17" s="49">
+        <f>H7*'Inputs'!H35</f>
+        <v/>
+      </c>
+      <c r="I17" s="49">
+        <f>I7*'Inputs'!I35</f>
+        <v/>
+      </c>
+      <c r="J17" s="49">
+        <f>J7*'Inputs'!J35</f>
+        <v/>
+      </c>
+      <c r="K17" s="49">
+        <f>K7*'Inputs'!K35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D17" s="46">
-        <f>D14+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="46">
-        <f>E14+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="46">
-        <f>F14+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="46">
-        <f>G14+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="46">
-        <f>H14+H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="46">
-        <f>I14+I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="46">
-        <f>J14+J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="46">
-        <f>K14+K16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="47" t="inlineStr">
+      <c r="D18" s="46">
+        <f>D15+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="46">
+        <f>E15+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="46">
+        <f>F15+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="46">
+        <f>G15+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="46">
+        <f>H15+H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="46">
+        <f>I15+I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="46">
+        <f>J15+J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="46">
+        <f>K15+K17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBITDA margin %</t>
         </is>
       </c>
-      <c r="D18" s="48">
-        <f>D17/D7</f>
-        <v/>
-      </c>
-      <c r="E18" s="48">
-        <f>E17/E7</f>
-        <v/>
-      </c>
-      <c r="F18" s="48">
-        <f>F17/F7</f>
-        <v/>
-      </c>
-      <c r="G18" s="48">
-        <f>G17/G7</f>
-        <v/>
-      </c>
-      <c r="H18" s="48">
-        <f>H17/H7</f>
-        <v/>
-      </c>
-      <c r="I18" s="48">
-        <f>I17/I7</f>
-        <v/>
-      </c>
-      <c r="J18" s="48">
-        <f>J17/J7</f>
-        <v/>
-      </c>
-      <c r="K18" s="48">
-        <f>K17/K7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="G19" s="45">
-        <f>'Inputs'!G44*('BS'!F7+'BS'!F8+'BS'!F15)</f>
-        <v/>
-      </c>
-      <c r="H19" s="45">
-        <f>'Inputs'!H44*('BS'!G7+'BS'!G8+'BS'!G15)</f>
-        <v/>
-      </c>
-      <c r="I19" s="45">
-        <f>'Inputs'!I44*('BS'!H7+'BS'!H8+'BS'!H15)</f>
-        <v/>
-      </c>
-      <c r="J19" s="45">
-        <f>'Inputs'!J44*('BS'!I7+'BS'!I8+'BS'!I15)</f>
-        <v/>
-      </c>
-      <c r="K19" s="45">
-        <f>'Inputs'!K44*('BS'!J7+'BS'!J8+'BS'!J15)</f>
+      <c r="D19" s="48">
+        <f>D18/D7</f>
+        <v/>
+      </c>
+      <c r="E19" s="48">
+        <f>E18/E7</f>
+        <v/>
+      </c>
+      <c r="F19" s="48">
+        <f>F18/F7</f>
+        <v/>
+      </c>
+      <c r="G19" s="48">
+        <f>G18/G7</f>
+        <v/>
+      </c>
+      <c r="H19" s="48">
+        <f>H18/H7</f>
+        <v/>
+      </c>
+      <c r="I19" s="48">
+        <f>I18/I7</f>
+        <v/>
+      </c>
+      <c r="J19" s="48">
+        <f>J18/J7</f>
+        <v/>
+      </c>
+      <c r="K19" s="48">
+        <f>K18/K7</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="G20" s="45">
-        <f>'Inputs'!G45*('BS'!F26+'BS'!F27+'BS'!F30)</f>
+        <f>'Inputs'!G45*('BS'!F7+'BS'!F8+'BS'!F15)</f>
         <v/>
       </c>
       <c r="H20" s="45">
-        <f>'Inputs'!H45*('BS'!G26+'BS'!G27+'BS'!G30)</f>
+        <f>'Inputs'!H45*('BS'!G7+'BS'!G8+'BS'!G15)</f>
         <v/>
       </c>
       <c r="I20" s="45">
-        <f>'Inputs'!I45*('BS'!H26+'BS'!H27+'BS'!H30)</f>
+        <f>'Inputs'!I45*('BS'!H7+'BS'!H8+'BS'!H15)</f>
         <v/>
       </c>
       <c r="J20" s="45">
-        <f>'Inputs'!J45*('BS'!I26+'BS'!I27+'BS'!I30)</f>
+        <f>'Inputs'!J45*('BS'!I7+'BS'!I8+'BS'!I15)</f>
         <v/>
       </c>
       <c r="K20" s="45">
-        <f>'Inputs'!K45*('BS'!J26+'BS'!J27+'BS'!J30)</f>
+        <f>'Inputs'!K45*('BS'!J7+'BS'!J8+'BS'!J15)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="24" t="inlineStr">
         <is>
+          <t>Interest expense (historical: as reported, memo)</t>
+        </is>
+      </c>
+      <c r="G21" s="45">
+        <f>'Inputs'!G46*('BS'!F26+'BS'!F27+'BS'!F28+'BS'!F31)</f>
+        <v/>
+      </c>
+      <c r="H21" s="45">
+        <f>'Inputs'!H46*('BS'!G26+'BS'!G27+'BS'!G28+'BS'!G31)</f>
+        <v/>
+      </c>
+      <c r="I21" s="45">
+        <f>'Inputs'!I46*('BS'!H26+'BS'!H27+'BS'!H28+'BS'!H31)</f>
+        <v/>
+      </c>
+      <c r="J21" s="45">
+        <f>'Inputs'!J46*('BS'!I26+'BS'!I27+'BS'!I28+'BS'!I31)</f>
+        <v/>
+      </c>
+      <c r="K21" s="45">
+        <f>'Inputs'!K46*('BS'!J26+'BS'!J27+'BS'!J28+'BS'!J31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
           <t>Other income / (expense), net</t>
         </is>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D22" s="44" t="n">
         <v>1156</v>
       </c>
-      <c r="E21" s="44" t="n">
+      <c r="E22" s="44" t="n">
         <v>980</v>
       </c>
-      <c r="F21" s="44" t="n">
+      <c r="F22" s="44" t="n">
         <v>1285</v>
       </c>
-      <c r="G21" s="50">
-        <f>G19-G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="50">
-        <f>H19-H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="50">
-        <f>I19-I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="50">
-        <f>J19-J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="50">
-        <f>K19-K20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="41" t="inlineStr">
+      <c r="G22" s="50">
+        <f>G20-G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="50">
+        <f>H20-H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="50">
+        <f>I20-I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="50">
+        <f>J20-J21</f>
+        <v/>
+      </c>
+      <c r="K22" s="50">
+        <f>K20-K21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>Income before taxes</t>
         </is>
       </c>
-      <c r="D22" s="46">
-        <f>D14+D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="46">
-        <f>E14+E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="46">
-        <f>F14+F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="46">
-        <f>G14+G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="46">
-        <f>H14+H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="46">
-        <f>I14+I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="46">
-        <f>J14+J21</f>
-        <v/>
-      </c>
-      <c r="K22" s="46">
-        <f>K14+K21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="24" t="inlineStr">
+      <c r="D23" s="46">
+        <f>D15+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="46">
+        <f>E15+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="46">
+        <f>F15+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="46">
+        <f>G15+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="46">
+        <f>H15+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="46">
+        <f>I15+I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="46">
+        <f>J15+J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="46">
+        <f>K15+K22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Provision for income taxes</t>
         </is>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D24" s="44" t="n">
         <v>13118</v>
       </c>
-      <c r="E23" s="44" t="n">
+      <c r="E24" s="44" t="n">
         <v>13973</v>
       </c>
-      <c r="F23" s="44" t="n">
+      <c r="F24" s="44" t="n">
         <v>19121</v>
       </c>
-      <c r="G23" s="45">
-        <f>G22*'Inputs'!G36</f>
-        <v/>
-      </c>
-      <c r="H23" s="45">
-        <f>H22*'Inputs'!H36</f>
-        <v/>
-      </c>
-      <c r="I23" s="45">
-        <f>I22*'Inputs'!I36</f>
-        <v/>
-      </c>
-      <c r="J23" s="45">
-        <f>J22*'Inputs'!J36</f>
-        <v/>
-      </c>
-      <c r="K23" s="45">
-        <f>K22*'Inputs'!K36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="41" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D24" s="51">
-        <f>D22-D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="51">
-        <f>E22-E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="51">
-        <f>F22-F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="51">
-        <f>G22-G23</f>
-        <v/>
-      </c>
-      <c r="H24" s="51">
-        <f>H22-H23</f>
-        <v/>
-      </c>
-      <c r="I24" s="51">
-        <f>I22-I23</f>
-        <v/>
-      </c>
-      <c r="J24" s="51">
-        <f>J22-J23</f>
-        <v/>
-      </c>
-      <c r="K24" s="51">
-        <f>K22-K23</f>
-        <v/>
+      <c r="G24" s="45">
+        <f>G23*'Inputs'!G37</f>
+        <v/>
+      </c>
+      <c r="H24" s="45">
+        <f>H23*'Inputs'!H37</f>
+        <v/>
+      </c>
+      <c r="I24" s="45">
+        <f>I23*'Inputs'!I37</f>
+        <v/>
+      </c>
+      <c r="J24" s="45">
+        <f>J23*'Inputs'!J37</f>
+        <v/>
+      </c>
+      <c r="K24" s="45">
+        <f>K23*'Inputs'!K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Equity income, minority interest &amp; other</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>Net income attributable to shareholders</t>
+        </is>
+      </c>
+      <c r="D26" s="51">
+        <f>D23-D24+D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="51">
+        <f>E23-E24+E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="51">
+        <f>F23-F24+F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="51">
+        <f>G23-G24+G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="51">
+        <f>H23-H24+H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="51">
+        <f>I23-I24+I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="51">
+        <f>J23-J24+J25</f>
+        <v/>
+      </c>
+      <c r="K26" s="51">
+        <f>K23-K24+K25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Diluted shares</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D28" s="52" t="n">
         <v>6521.634</v>
       </c>
-      <c r="E26" s="52" t="n">
+      <c r="E28" s="52" t="n">
         <v>6122.663</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F28" s="52" t="n">
         <v>5793.069</v>
       </c>
-      <c r="G26" s="53">
+      <c r="G28" s="53">
         <f>'Inputs'!$D$23</f>
         <v/>
       </c>
-      <c r="H26" s="53">
+      <c r="H28" s="53">
         <f>'Inputs'!$D$23</f>
         <v/>
       </c>
-      <c r="I26" s="53">
+      <c r="I28" s="53">
         <f>'Inputs'!$D$23</f>
         <v/>
       </c>
-      <c r="J26" s="53">
+      <c r="J28" s="53">
         <f>'Inputs'!$D$23</f>
         <v/>
       </c>
-      <c r="K26" s="53">
+      <c r="K28" s="53">
         <f>'Inputs'!$D$23</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="24" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="D27" s="54">
-        <f>D24/D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="54">
-        <f>E24/E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="54">
-        <f>F24/F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="54">
-        <f>G24/G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="54">
-        <f>H24/H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="54">
-        <f>I24/I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="54">
-        <f>J24/J26</f>
-        <v/>
-      </c>
-      <c r="K27" s="54">
-        <f>K24/K26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="D29" s="54">
+        <f>D26/D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="54">
+        <f>E26/E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="54">
+        <f>F26/F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="54">
+        <f>G26/G28</f>
+        <v/>
+      </c>
+      <c r="H29" s="54">
+        <f>H26/H28</f>
+        <v/>
+      </c>
+      <c r="I29" s="54">
+        <f>I26/I28</f>
+        <v/>
+      </c>
+      <c r="J29" s="54">
+        <f>J26/J28</f>
+        <v/>
+      </c>
+      <c r="K29" s="54">
+        <f>K26/K28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Net sales by segment (reported)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="23" t="n"/>
-      <c r="I29" s="23" t="n"/>
-      <c r="J29" s="23" t="n"/>
-      <c r="K29" s="23" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Americas</t>
-        </is>
-      </c>
-      <c r="D30" s="44" t="n">
-        <v>77093</v>
-      </c>
-      <c r="E30" s="44" t="n">
-        <v>80095</v>
-      </c>
-      <c r="F30" s="44" t="n">
-        <v>93864</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="D31" s="44" t="n">
-        <v>40980</v>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>44285</v>
-      </c>
-      <c r="F31" s="44" t="n">
-        <v>50337</v>
-      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Greater China</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="D32" s="44" t="n">
-        <v>27016</v>
+        <v>77093</v>
       </c>
       <c r="E32" s="44" t="n">
-        <v>31853</v>
+        <v>80095</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>58715</v>
+        <v>93864</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="D33" s="44" t="n">
-        <v>13782</v>
+        <v>40980</v>
       </c>
       <c r="E33" s="44" t="n">
-        <v>15314</v>
+        <v>44285</v>
       </c>
       <c r="F33" s="44" t="n">
-        <v>15706</v>
+        <v>50337</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="24" t="inlineStr">
         <is>
+          <t>Greater China</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="n">
+        <v>27016</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>31853</v>
+      </c>
+      <c r="F34" s="44" t="n">
+        <v>58715</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="n">
+        <v>13782</v>
+      </c>
+      <c r="E35" s="44" t="n">
+        <v>15314</v>
+      </c>
+      <c r="F35" s="44" t="n">
+        <v>15706</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="24" t="inlineStr">
+        <is>
           <t>Rest of Asia Pacific</t>
         </is>
       </c>
-      <c r="D34" s="44" t="n">
+      <c r="D36" s="44" t="n">
         <v>12039</v>
       </c>
-      <c r="E34" s="44" t="n">
+      <c r="E36" s="44" t="n">
         <v>11248</v>
       </c>
-      <c r="F34" s="44" t="n">
+      <c r="F36" s="44" t="n">
         <v>15093</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="41" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D35" s="46">
-        <f>SUM(D30:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="46">
-        <f>SUM(E30:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="46">
-        <f>SUM(F30:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="55" t="inlineStr">
+      <c r="D37" s="46">
+        <f>SUM(D32:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="46">
+        <f>SUM(E32:E36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="46">
+        <f>SUM(F32:F36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="55" t="inlineStr">
         <is>
           <t>Check: segments - net sales</t>
         </is>
       </c>
-      <c r="D36" s="56">
-        <f>D35-D7</f>
-        <v/>
-      </c>
-      <c r="E36" s="56">
-        <f>E35-E7</f>
-        <v/>
-      </c>
-      <c r="F36" s="56">
-        <f>F35-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="23" t="inlineStr">
+      <c r="D38" s="56">
+        <f>D37-D7</f>
+        <v/>
+      </c>
+      <c r="E38" s="56">
+        <f>E37-E7</f>
+        <v/>
+      </c>
+      <c r="F38" s="56">
+        <f>F37-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>Net sales by product (reported)</t>
         </is>
       </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="23" t="n"/>
-      <c r="H38" s="23" t="n"/>
-      <c r="I38" s="23" t="n"/>
-      <c r="J38" s="23" t="n"/>
-      <c r="K38" s="23" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>iPhone</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="n">
-        <v>91279</v>
-      </c>
-      <c r="E39" s="44" t="n">
-        <v>101991</v>
-      </c>
-      <c r="F39" s="44" t="n">
-        <v>155041</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>iPad</t>
-        </is>
-      </c>
-      <c r="D40" s="44" t="n">
-        <v>31980</v>
-      </c>
-      <c r="E40" s="44" t="n">
-        <v>30283</v>
-      </c>
-      <c r="F40" s="44" t="n">
-        <v>23227</v>
-      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="n"/>
+      <c r="H40" s="23" t="n"/>
+      <c r="I40" s="23" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>Mac</t>
+          <t>iPhone</t>
         </is>
       </c>
       <c r="D41" s="44" t="n">
-        <v>21483</v>
+        <v>91279</v>
       </c>
       <c r="E41" s="44" t="n">
-        <v>24079</v>
+        <v>101991</v>
       </c>
       <c r="F41" s="44" t="n">
-        <v>25471</v>
+        <v>155041</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>iPad</t>
         </is>
       </c>
       <c r="D42" s="44" t="n">
-        <v>16051</v>
+        <v>31980</v>
       </c>
       <c r="E42" s="44" t="n">
-        <v>18063</v>
+        <v>30283</v>
       </c>
       <c r="F42" s="44" t="n">
-        <v>19909</v>
+        <v>23227</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="24" t="inlineStr">
         <is>
+          <t>Mac</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="n">
+        <v>21483</v>
+      </c>
+      <c r="E43" s="44" t="n">
+        <v>24079</v>
+      </c>
+      <c r="F43" s="44" t="n">
+        <v>25471</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="n">
+        <v>16051</v>
+      </c>
+      <c r="E44" s="44" t="n">
+        <v>18063</v>
+      </c>
+      <c r="F44" s="44" t="n">
+        <v>19909</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="24" t="inlineStr">
+        <is>
           <t>Other Products</t>
         </is>
       </c>
-      <c r="D43" s="44" t="n">
+      <c r="D45" s="44" t="n">
         <v>10117</v>
       </c>
-      <c r="E43" s="44" t="n">
+      <c r="E45" s="44" t="n">
         <v>8379</v>
       </c>
-      <c r="F43" s="44" t="n">
+      <c r="F45" s="44" t="n">
         <v>10067</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="41" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D44" s="46">
-        <f>SUM(D39:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="46">
-        <f>SUM(E39:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="46">
-        <f>SUM(F39:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="55" t="inlineStr">
+      <c r="D46" s="46">
+        <f>SUM(D41:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="46">
+        <f>SUM(E41:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="46">
+        <f>SUM(F41:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>Check: segments - net sales</t>
         </is>
       </c>
-      <c r="D45" s="56">
-        <f>D44-D7</f>
-        <v/>
-      </c>
-      <c r="E45" s="56">
-        <f>E44-E7</f>
-        <v/>
-      </c>
-      <c r="F45" s="56">
-        <f>F44-F7</f>
+      <c r="D47" s="56">
+        <f>D46-D7</f>
+        <v/>
+      </c>
+      <c r="E47" s="56">
+        <f>E46-E7</f>
+        <v/>
+      </c>
+      <c r="F47" s="56">
+        <f>F46-F7</f>
         <v/>
       </c>
     </row>
@@ -4377,1273 +4470,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:K45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Apple Inc.: Balance Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>USD in millions, except per-share data. Blue = input / reported, black = formula, green = link to another sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="18" t="inlineStr">
-        <is>
-          <t>Projected</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="19" t="n"/>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="19" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Fiscal year ending September</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="21" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>2015</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>2016</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>2017</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>2019</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n"/>
-      <c r="I6" s="23" t="n"/>
-      <c r="J6" s="23" t="n"/>
-      <c r="K6" s="23" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="E7" s="44" t="n">
-        <v>13844</v>
-      </c>
-      <c r="F7" s="44" t="n">
-        <v>21120</v>
-      </c>
-      <c r="G7" s="45">
-        <f>'CFS'!G46</f>
-        <v/>
-      </c>
-      <c r="H7" s="45">
-        <f>'CFS'!H46</f>
-        <v/>
-      </c>
-      <c r="I7" s="45">
-        <f>'CFS'!I46</f>
-        <v/>
-      </c>
-      <c r="J7" s="45">
-        <f>'CFS'!J46</f>
-        <v/>
-      </c>
-      <c r="K7" s="45">
-        <f>'CFS'!K46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Short-term marketable securities</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="n">
-        <v>11233</v>
-      </c>
-      <c r="F8" s="44" t="n">
-        <v>20481</v>
-      </c>
-      <c r="G8" s="50">
-        <f>F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="50">
-        <f>G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="50">
-        <f>H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="50">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="50">
-        <f>J8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="E9" s="44" t="n">
-        <v>17460</v>
-      </c>
-      <c r="F9" s="44" t="n">
-        <v>16849</v>
-      </c>
-      <c r="G9" s="45">
-        <f>'IS'!G7*'Inputs'!G37/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="H9" s="45">
-        <f>'IS'!H7*'Inputs'!H37/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="I9" s="45">
-        <f>'IS'!I7*'Inputs'!I37/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="J9" s="45">
-        <f>'IS'!J7*'Inputs'!J37/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="K9" s="45">
-        <f>'IS'!K7*'Inputs'!K37/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="E10" s="44" t="n">
-        <v>2111</v>
-      </c>
-      <c r="F10" s="44" t="n">
-        <v>2349</v>
-      </c>
-      <c r="G10" s="45">
-        <f>'IS'!G8*'Inputs'!G38/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="H10" s="45">
-        <f>'IS'!H8*'Inputs'!H38/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="I10" s="45">
-        <f>'IS'!I8*'Inputs'!I38/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="J10" s="45">
-        <f>'IS'!J8*'Inputs'!J38/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="K10" s="45">
-        <f>'IS'!K8*'Inputs'!K38/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Deferred tax assets</t>
-        </is>
-      </c>
-      <c r="E11" s="44" t="n">
-        <v>4318</v>
-      </c>
-      <c r="F11" s="44" t="n">
-        <v>5546</v>
-      </c>
-      <c r="G11" s="50">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="50">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="50">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="50">
-        <f>I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="50">
-        <f>J11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Vendor non-trade receivables</t>
-        </is>
-      </c>
-      <c r="E12" s="44" t="n">
-        <v>9759</v>
-      </c>
-      <c r="F12" s="44" t="n">
-        <v>13494</v>
-      </c>
-      <c r="G12" s="45">
-        <f>'IS'!G7*'Inputs'!G40</f>
-        <v/>
-      </c>
-      <c r="H12" s="45">
-        <f>'IS'!H7*'Inputs'!H40</f>
-        <v/>
-      </c>
-      <c r="I12" s="45">
-        <f>'IS'!I7*'Inputs'!I40</f>
-        <v/>
-      </c>
-      <c r="J12" s="45">
-        <f>'IS'!J7*'Inputs'!J40</f>
-        <v/>
-      </c>
-      <c r="K12" s="45">
-        <f>'IS'!K7*'Inputs'!K40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Other current assets</t>
-        </is>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>9806</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <v>9539</v>
-      </c>
-      <c r="G13" s="45">
-        <f>'IS'!G7*'Inputs'!G41</f>
-        <v/>
-      </c>
-      <c r="H13" s="45">
-        <f>'IS'!H7*'Inputs'!H41</f>
-        <v/>
-      </c>
-      <c r="I13" s="45">
-        <f>'IS'!I7*'Inputs'!I41</f>
-        <v/>
-      </c>
-      <c r="J13" s="45">
-        <f>'IS'!J7*'Inputs'!J41</f>
-        <v/>
-      </c>
-      <c r="K13" s="45">
-        <f>'IS'!K7*'Inputs'!K41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="E14" s="46">
-        <f>SUM(E7:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="46">
-        <f>SUM(F7:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="46">
-        <f>SUM(G7:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="46">
-        <f>SUM(H7:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="46">
-        <f>SUM(I7:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="46">
-        <f>SUM(J7:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="46">
-        <f>SUM(K7:K13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Long-term marketable securities</t>
-        </is>
-      </c>
-      <c r="E15" s="44" t="n">
-        <v>130162</v>
-      </c>
-      <c r="F15" s="44" t="n">
-        <v>164065</v>
-      </c>
-      <c r="G15" s="50">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="50">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="50">
-        <f>H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="50">
-        <f>I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="50">
-        <f>J15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment, net</t>
-        </is>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>20624</v>
-      </c>
-      <c r="F16" s="44" t="n">
-        <v>22471</v>
-      </c>
-      <c r="G16" s="45">
-        <f>F16-'CFS'!G28-'IS'!G16</f>
-        <v/>
-      </c>
-      <c r="H16" s="45">
-        <f>G16-'CFS'!H28-'IS'!H16</f>
-        <v/>
-      </c>
-      <c r="I16" s="45">
-        <f>H16-'CFS'!I28-'IS'!I16</f>
-        <v/>
-      </c>
-      <c r="J16" s="45">
-        <f>I16-'CFS'!J28-'IS'!J16</f>
-        <v/>
-      </c>
-      <c r="K16" s="45">
-        <f>J16-'CFS'!K28-'IS'!K16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>4616</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>5116</v>
-      </c>
-      <c r="G17" s="50">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="50">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="50">
-        <f>H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="50">
-        <f>I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="50">
-        <f>J17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Acquired intangible assets, net</t>
-        </is>
-      </c>
-      <c r="E18" s="44" t="n">
-        <v>4142</v>
-      </c>
-      <c r="F18" s="44" t="n">
-        <v>3893</v>
-      </c>
-      <c r="G18" s="50">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="50">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="50">
-        <f>H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="50">
-        <f>I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="50">
-        <f>J18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Other assets</t>
-        </is>
-      </c>
-      <c r="E19" s="44" t="n">
-        <v>3764</v>
-      </c>
-      <c r="F19" s="44" t="n">
-        <v>5556</v>
-      </c>
-      <c r="G19" s="50">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="50">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="50">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="50">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="50">
-        <f>J19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="41" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="E20" s="51">
-        <f>E14+SUM(E15:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="51">
-        <f>F14+SUM(F15:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="51">
-        <f>G14+SUM(G15:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="51">
-        <f>H14+SUM(H15:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="51">
-        <f>I14+SUM(I15:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="51">
-        <f>J14+SUM(J15:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="51">
-        <f>K14+SUM(K15:K19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="23" t="n"/>
-      <c r="I22" s="23" t="n"/>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="23" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="E23" s="44" t="n">
-        <v>30196</v>
-      </c>
-      <c r="F23" s="44" t="n">
-        <v>35490</v>
-      </c>
-      <c r="G23" s="45">
-        <f>'IS'!G8*'Inputs'!G39/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="H23" s="45">
-        <f>'IS'!H8*'Inputs'!H39/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="I23" s="45">
-        <f>'IS'!I8*'Inputs'!I39/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="J23" s="45">
-        <f>'IS'!J8*'Inputs'!J39/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-      <c r="K23" s="45">
-        <f>'IS'!K8*'Inputs'!K39/'Inputs'!$D$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Accrued expenses</t>
-        </is>
-      </c>
-      <c r="E24" s="44" t="n">
-        <v>18453</v>
-      </c>
-      <c r="F24" s="44" t="n">
-        <v>25181</v>
-      </c>
-      <c r="G24" s="45">
-        <f>'IS'!G7*'Inputs'!G42</f>
-        <v/>
-      </c>
-      <c r="H24" s="45">
-        <f>'IS'!H7*'Inputs'!H42</f>
-        <v/>
-      </c>
-      <c r="I24" s="45">
-        <f>'IS'!I7*'Inputs'!I42</f>
-        <v/>
-      </c>
-      <c r="J24" s="45">
-        <f>'IS'!J7*'Inputs'!J42</f>
-        <v/>
-      </c>
-      <c r="K24" s="45">
-        <f>'IS'!K7*'Inputs'!K42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>8491</v>
-      </c>
-      <c r="F25" s="44" t="n">
-        <v>8940</v>
-      </c>
-      <c r="G25" s="45">
-        <f>'IS'!G7*'Inputs'!G43</f>
-        <v/>
-      </c>
-      <c r="H25" s="45">
-        <f>'IS'!H7*'Inputs'!H43</f>
-        <v/>
-      </c>
-      <c r="I25" s="45">
-        <f>'IS'!I7*'Inputs'!I43</f>
-        <v/>
-      </c>
-      <c r="J25" s="45">
-        <f>'IS'!J7*'Inputs'!J43</f>
-        <v/>
-      </c>
-      <c r="K25" s="45">
-        <f>'IS'!K7*'Inputs'!K43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Commercial paper</t>
-        </is>
-      </c>
-      <c r="E26" s="44" t="n">
-        <v>6308</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>8499</v>
-      </c>
-      <c r="G26" s="50">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H26" s="50">
-        <f>G26</f>
-        <v/>
-      </c>
-      <c r="I26" s="50">
-        <f>H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="50">
-        <f>I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="50">
-        <f>J26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>Current portion of long-term debt</t>
-        </is>
-      </c>
-      <c r="E27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="44" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G27" s="50">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H27" s="50">
-        <f>G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="50">
-        <f>H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="50">
-        <f>I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="50">
-        <f>J27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>Total current liabilities</t>
-        </is>
-      </c>
-      <c r="E28" s="46">
-        <f>SUM(E23:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="46">
-        <f>SUM(F23:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="46">
-        <f>SUM(G23:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="46">
-        <f>SUM(H23:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="46">
-        <f>SUM(I23:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="46">
-        <f>SUM(J23:J27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="46">
-        <f>SUM(K23:K27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Deferred revenue, non-current</t>
-        </is>
-      </c>
-      <c r="E29" s="44" t="n">
-        <v>3031</v>
-      </c>
-      <c r="F29" s="44" t="n">
-        <v>3624</v>
-      </c>
-      <c r="G29" s="50">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="H29" s="50">
-        <f>G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="50">
-        <f>H29</f>
-        <v/>
-      </c>
-      <c r="J29" s="50">
-        <f>I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="50">
-        <f>J29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Long-term debt</t>
-        </is>
-      </c>
-      <c r="E30" s="44" t="n">
-        <v>28987</v>
-      </c>
-      <c r="F30" s="44" t="n">
-        <v>53463</v>
-      </c>
-      <c r="G30" s="50">
-        <f>F30</f>
-        <v/>
-      </c>
-      <c r="H30" s="50">
-        <f>G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="50">
-        <f>H30</f>
-        <v/>
-      </c>
-      <c r="J30" s="50">
-        <f>I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="50">
-        <f>J30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>Other non-current liabilities</t>
-        </is>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>24826</v>
-      </c>
-      <c r="F31" s="44" t="n">
-        <v>33427</v>
-      </c>
-      <c r="G31" s="50">
-        <f>F31</f>
-        <v/>
-      </c>
-      <c r="H31" s="50">
-        <f>G31</f>
-        <v/>
-      </c>
-      <c r="I31" s="50">
-        <f>H31</f>
-        <v/>
-      </c>
-      <c r="J31" s="50">
-        <f>I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="50">
-        <f>J31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="41" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="E32" s="46">
-        <f>E28+SUM(E29:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="46">
-        <f>F28+SUM(F29:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="46">
-        <f>G28+SUM(G29:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="46">
-        <f>H28+SUM(H29:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="46">
-        <f>I28+SUM(I29:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="46">
-        <f>J28+SUM(J29:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="46">
-        <f>K28+SUM(K29:K31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Shareholders' equity</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
-      <c r="I34" s="23" t="n"/>
-      <c r="J34" s="23" t="n"/>
-      <c r="K34" s="23" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Common stock and additional paid-in capital</t>
-        </is>
-      </c>
-      <c r="E35" s="44" t="n">
-        <v>23313</v>
-      </c>
-      <c r="F35" s="44" t="n">
-        <v>27416</v>
-      </c>
-      <c r="G35" s="50">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="H35" s="50">
-        <f>G35</f>
-        <v/>
-      </c>
-      <c r="I35" s="50">
-        <f>H35</f>
-        <v/>
-      </c>
-      <c r="J35" s="50">
-        <f>I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="50">
-        <f>J35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="E36" s="44" t="n">
-        <v>87152</v>
-      </c>
-      <c r="F36" s="44" t="n">
-        <v>92284</v>
-      </c>
-      <c r="G36" s="45">
-        <f>F36+'IS'!G24+'CFS'!G37+'CFS'!G38</f>
-        <v/>
-      </c>
-      <c r="H36" s="45">
-        <f>G36+'IS'!H24+'CFS'!H37+'CFS'!H38</f>
-        <v/>
-      </c>
-      <c r="I36" s="45">
-        <f>H36+'IS'!I24+'CFS'!I37+'CFS'!I38</f>
-        <v/>
-      </c>
-      <c r="J36" s="45">
-        <f>I36+'IS'!J24+'CFS'!J37+'CFS'!J38</f>
-        <v/>
-      </c>
-      <c r="K36" s="45">
-        <f>J36+'IS'!K24+'CFS'!K37+'CFS'!K38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>Accumulated other comprehensive income</t>
-        </is>
-      </c>
-      <c r="E37" s="44" t="n">
-        <v>1082</v>
-      </c>
-      <c r="F37" s="44" t="n">
-        <v>-345</v>
-      </c>
-      <c r="G37" s="50">
-        <f>F37</f>
-        <v/>
-      </c>
-      <c r="H37" s="50">
-        <f>G37</f>
-        <v/>
-      </c>
-      <c r="I37" s="50">
-        <f>H37</f>
-        <v/>
-      </c>
-      <c r="J37" s="50">
-        <f>I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="50">
-        <f>J37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="41" t="inlineStr">
-        <is>
-          <t>Total shareholders' equity</t>
-        </is>
-      </c>
-      <c r="E38" s="46">
-        <f>SUM(E35:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="46">
-        <f>SUM(F35:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="46">
-        <f>SUM(G35:G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="46">
-        <f>SUM(H35:H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="46">
-        <f>SUM(I35:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="46">
-        <f>SUM(J35:J37)</f>
-        <v/>
-      </c>
-      <c r="K38" s="46">
-        <f>SUM(K35:K37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>Total liabilities and shareholders' equity</t>
-        </is>
-      </c>
-      <c r="E39" s="51">
-        <f>E32+E38</f>
-        <v/>
-      </c>
-      <c r="F39" s="51">
-        <f>F32+F38</f>
-        <v/>
-      </c>
-      <c r="G39" s="51">
-        <f>G32+G38</f>
-        <v/>
-      </c>
-      <c r="H39" s="51">
-        <f>H32+H38</f>
-        <v/>
-      </c>
-      <c r="I39" s="51">
-        <f>I32+I38</f>
-        <v/>
-      </c>
-      <c r="J39" s="51">
-        <f>J32+J38</f>
-        <v/>
-      </c>
-      <c r="K39" s="51">
-        <f>K32+K38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="55" t="inlineStr">
-        <is>
-          <t>Check: Assets - (Liabilities + Equity)</t>
-        </is>
-      </c>
-      <c r="E40" s="56">
-        <f>E20-E39</f>
-        <v/>
-      </c>
-      <c r="F40" s="56">
-        <f>F20-F39</f>
-        <v/>
-      </c>
-      <c r="G40" s="56">
-        <f>G20-G39</f>
-        <v/>
-      </c>
-      <c r="H40" s="56">
-        <f>H20-H39</f>
-        <v/>
-      </c>
-      <c r="I40" s="56">
-        <f>I20-I39</f>
-        <v/>
-      </c>
-      <c r="J40" s="56">
-        <f>J20-J39</f>
-        <v/>
-      </c>
-      <c r="K40" s="56">
-        <f>K20-K39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Memo</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="23" t="n"/>
-      <c r="I42" s="23" t="n"/>
-      <c r="J42" s="23" t="n"/>
-      <c r="K42" s="23" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>Net working capital (operating)</t>
-        </is>
-      </c>
-      <c r="E43" s="50">
-        <f>(E14-E7-E8-E11)-(E28-E26-E27)</f>
-        <v/>
-      </c>
-      <c r="F43" s="50">
-        <f>(F14-F7-F8-F11)-(F28-F26-F27)</f>
-        <v/>
-      </c>
-      <c r="G43" s="50">
-        <f>(G14-G7-G8-G11)-(G28-G26-G27)</f>
-        <v/>
-      </c>
-      <c r="H43" s="50">
-        <f>(H14-H7-H8-H11)-(H28-H26-H27)</f>
-        <v/>
-      </c>
-      <c r="I43" s="50">
-        <f>(I14-I7-I8-I11)-(I28-I26-I27)</f>
-        <v/>
-      </c>
-      <c r="J43" s="50">
-        <f>(J14-J7-J8-J11)-(J28-J26-J27)</f>
-        <v/>
-      </c>
-      <c r="K43" s="50">
-        <f>(K14-K7-K8-K11)-(K28-K26-K27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>Total debt</t>
-        </is>
-      </c>
-      <c r="E44" s="50">
-        <f>E26+E27+E30</f>
-        <v/>
-      </c>
-      <c r="F44" s="50">
-        <f>F26+F27+F30</f>
-        <v/>
-      </c>
-      <c r="G44" s="50">
-        <f>G26+G27+G30</f>
-        <v/>
-      </c>
-      <c r="H44" s="50">
-        <f>H26+H27+H30</f>
-        <v/>
-      </c>
-      <c r="I44" s="50">
-        <f>I26+I27+I30</f>
-        <v/>
-      </c>
-      <c r="J44" s="50">
-        <f>J26+J27+J30</f>
-        <v/>
-      </c>
-      <c r="K44" s="50">
-        <f>K26+K27+K30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Cash and marketable securities</t>
-        </is>
-      </c>
-      <c r="E45" s="50">
-        <f>E7+E8+E15</f>
-        <v/>
-      </c>
-      <c r="F45" s="50">
-        <f>F7+F8+F15</f>
-        <v/>
-      </c>
-      <c r="G45" s="50">
-        <f>G7+G8+G15</f>
-        <v/>
-      </c>
-      <c r="H45" s="50">
-        <f>H7+H8+H15</f>
-        <v/>
-      </c>
-      <c r="I45" s="50">
-        <f>I7+I8+I15</f>
-        <v/>
-      </c>
-      <c r="J45" s="50">
-        <f>J7+J8+J15</f>
-        <v/>
-      </c>
-      <c r="K45" s="50">
-        <f>K7+K8+K15</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="E3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5669,6 +4495,1372 @@
     <row r="1">
       <c r="B1" s="14" t="inlineStr">
         <is>
+          <t>Apple Inc.: Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>USD in millions, except per-share data. Blue = input / reported, black = formula, green = link to another sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>Projected</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="n"/>
+      <c r="I3" s="19" t="n"/>
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="19" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Fiscal year ending September</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="21" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H4" s="22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>13844</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <v>21120</v>
+      </c>
+      <c r="G7" s="45">
+        <f>'CFS'!G47</f>
+        <v/>
+      </c>
+      <c r="H7" s="45">
+        <f>'CFS'!H47</f>
+        <v/>
+      </c>
+      <c r="I7" s="45">
+        <f>'CFS'!I47</f>
+        <v/>
+      </c>
+      <c r="J7" s="45">
+        <f>'CFS'!J47</f>
+        <v/>
+      </c>
+      <c r="K7" s="45">
+        <f>'CFS'!K47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Short-term marketable securities</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>11233</v>
+      </c>
+      <c r="F8" s="44" t="n">
+        <v>20481</v>
+      </c>
+      <c r="G8" s="50">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="50">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="50">
+        <f>H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="50">
+        <f>I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="50">
+        <f>J8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>17460</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>16849</v>
+      </c>
+      <c r="G9" s="45">
+        <f>'IS'!G7*'Inputs'!G38/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="H9" s="45">
+        <f>'IS'!H7*'Inputs'!H38/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="I9" s="45">
+        <f>'IS'!I7*'Inputs'!I38/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="J9" s="45">
+        <f>'IS'!J7*'Inputs'!J38/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="K9" s="45">
+        <f>'IS'!K7*'Inputs'!K38/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>2111</v>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>2349</v>
+      </c>
+      <c r="G10" s="45">
+        <f>'IS'!G8*'Inputs'!G39/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="H10" s="45">
+        <f>'IS'!H8*'Inputs'!H39/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="I10" s="45">
+        <f>'IS'!I8*'Inputs'!I39/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="J10" s="45">
+        <f>'IS'!J8*'Inputs'!J39/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="K10" s="45">
+        <f>'IS'!K8*'Inputs'!K39/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>4318</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>5546</v>
+      </c>
+      <c r="G11" s="50">
+        <f>F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="50">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="50">
+        <f>H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="50">
+        <f>I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="50">
+        <f>J11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Vendor non-trade receivables</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>9759</v>
+      </c>
+      <c r="F12" s="44" t="n">
+        <v>13494</v>
+      </c>
+      <c r="G12" s="45">
+        <f>'IS'!G7*'Inputs'!G41</f>
+        <v/>
+      </c>
+      <c r="H12" s="45">
+        <f>'IS'!H7*'Inputs'!H41</f>
+        <v/>
+      </c>
+      <c r="I12" s="45">
+        <f>'IS'!I7*'Inputs'!I41</f>
+        <v/>
+      </c>
+      <c r="J12" s="45">
+        <f>'IS'!J7*'Inputs'!J41</f>
+        <v/>
+      </c>
+      <c r="K12" s="45">
+        <f>'IS'!K7*'Inputs'!K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Other current assets</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>9806</v>
+      </c>
+      <c r="F13" s="44" t="n">
+        <v>9539</v>
+      </c>
+      <c r="G13" s="45">
+        <f>'IS'!G7*'Inputs'!G42</f>
+        <v/>
+      </c>
+      <c r="H13" s="45">
+        <f>'IS'!H7*'Inputs'!H42</f>
+        <v/>
+      </c>
+      <c r="I13" s="45">
+        <f>'IS'!I7*'Inputs'!I42</f>
+        <v/>
+      </c>
+      <c r="J13" s="45">
+        <f>'IS'!J7*'Inputs'!J42</f>
+        <v/>
+      </c>
+      <c r="K13" s="45">
+        <f>'IS'!K7*'Inputs'!K42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Total current assets</t>
+        </is>
+      </c>
+      <c r="E14" s="46">
+        <f>SUM(E7:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="46">
+        <f>SUM(F7:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="46">
+        <f>SUM(G7:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="46">
+        <f>SUM(H7:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="46">
+        <f>SUM(I7:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="46">
+        <f>SUM(J7:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>SUM(K7:K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Long-term marketable securities</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="n">
+        <v>130162</v>
+      </c>
+      <c r="F15" s="44" t="n">
+        <v>164065</v>
+      </c>
+      <c r="G15" s="50">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="50">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="50">
+        <f>H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="50">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="50">
+        <f>J15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment, net</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n">
+        <v>20624</v>
+      </c>
+      <c r="F16" s="44" t="n">
+        <v>22471</v>
+      </c>
+      <c r="G16" s="45">
+        <f>MAX(F16-'CFS'!G28-'IS'!G17,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="45">
+        <f>MAX(G16-'CFS'!H28-'IS'!H17,0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="45">
+        <f>MAX(H16-'CFS'!I28-'IS'!I17,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="45">
+        <f>MAX(I16-'CFS'!J28-'IS'!J17,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="45">
+        <f>MAX(J16-'CFS'!K28-'IS'!K17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>4616</v>
+      </c>
+      <c r="F17" s="44" t="n">
+        <v>5116</v>
+      </c>
+      <c r="G17" s="50">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="50">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="50">
+        <f>H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="50">
+        <f>I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="50">
+        <f>J17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Acquired intangible assets, net</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F18" s="44" t="n">
+        <v>3893</v>
+      </c>
+      <c r="G18" s="45">
+        <f>F18-MIN(MAX('IS'!G17+'CFS'!G28-F16,0),F18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="45">
+        <f>G18-MIN(MAX('IS'!H17+'CFS'!H28-G16,0),G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="45">
+        <f>H18-MIN(MAX('IS'!I17+'CFS'!I28-H16,0),H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="45">
+        <f>I18-MIN(MAX('IS'!J17+'CFS'!J28-I16,0),I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="45">
+        <f>J18-MIN(MAX('IS'!K17+'CFS'!K28-J16,0),J18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>3764</v>
+      </c>
+      <c r="F19" s="44" t="n">
+        <v>5556</v>
+      </c>
+      <c r="G19" s="45">
+        <f>F19-MAX(MAX('IS'!G17+'CFS'!G28-F16,0)-F18,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="45">
+        <f>G19-MAX(MAX('IS'!H17+'CFS'!H28-G16,0)-G18,0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="45">
+        <f>H19-MAX(MAX('IS'!I17+'CFS'!I28-H16,0)-H18,0)</f>
+        <v/>
+      </c>
+      <c r="J19" s="45">
+        <f>I19-MAX(MAX('IS'!J17+'CFS'!J28-I16,0)-I18,0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="45">
+        <f>J19-MAX(MAX('IS'!K17+'CFS'!K28-J16,0)-J18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="E20" s="51">
+        <f>E14+SUM(E15:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="51">
+        <f>F14+SUM(F15:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="51">
+        <f>G14+SUM(G15:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="51">
+        <f>H14+SUM(H15:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="51">
+        <f>I14+SUM(I15:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="51">
+        <f>J14+SUM(J15:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="51">
+        <f>K14+SUM(K15:K19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>30196</v>
+      </c>
+      <c r="F23" s="44" t="n">
+        <v>35490</v>
+      </c>
+      <c r="G23" s="45">
+        <f>'IS'!G8*'Inputs'!G40/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="H23" s="45">
+        <f>'IS'!H8*'Inputs'!H40/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="I23" s="45">
+        <f>'IS'!I8*'Inputs'!I40/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="J23" s="45">
+        <f>'IS'!J8*'Inputs'!J40/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+      <c r="K23" s="45">
+        <f>'IS'!K8*'Inputs'!K40/'Inputs'!$D$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Accrued and other current liabilities</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>18453</v>
+      </c>
+      <c r="F24" s="44" t="n">
+        <v>25181</v>
+      </c>
+      <c r="G24" s="45">
+        <f>'IS'!G7*'Inputs'!G43</f>
+        <v/>
+      </c>
+      <c r="H24" s="45">
+        <f>'IS'!H7*'Inputs'!H43</f>
+        <v/>
+      </c>
+      <c r="I24" s="45">
+        <f>'IS'!I7*'Inputs'!I43</f>
+        <v/>
+      </c>
+      <c r="J24" s="45">
+        <f>'IS'!J7*'Inputs'!J43</f>
+        <v/>
+      </c>
+      <c r="K24" s="45">
+        <f>'IS'!K7*'Inputs'!K43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>8491</v>
+      </c>
+      <c r="F25" s="44" t="n">
+        <v>8940</v>
+      </c>
+      <c r="G25" s="45">
+        <f>'IS'!G7*'Inputs'!G44</f>
+        <v/>
+      </c>
+      <c r="H25" s="45">
+        <f>'IS'!H7*'Inputs'!H44</f>
+        <v/>
+      </c>
+      <c r="I25" s="45">
+        <f>'IS'!I7*'Inputs'!I44</f>
+        <v/>
+      </c>
+      <c r="J25" s="45">
+        <f>'IS'!J7*'Inputs'!J44</f>
+        <v/>
+      </c>
+      <c r="K25" s="45">
+        <f>'IS'!K7*'Inputs'!K44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Commercial paper</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>6308</v>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>8499</v>
+      </c>
+      <c r="G26" s="50">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="50">
+        <f>G26</f>
+        <v/>
+      </c>
+      <c r="I26" s="50">
+        <f>H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="50">
+        <f>I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="50">
+        <f>J26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>Short-term borrowings (incl. revolver draws)</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="45">
+        <f>F27+'CFS'!G39</f>
+        <v/>
+      </c>
+      <c r="H27" s="45">
+        <f>G27+'CFS'!H39</f>
+        <v/>
+      </c>
+      <c r="I27" s="45">
+        <f>H27+'CFS'!I39</f>
+        <v/>
+      </c>
+      <c r="J27" s="45">
+        <f>I27+'CFS'!J39</f>
+        <v/>
+      </c>
+      <c r="K27" s="45">
+        <f>J27+'CFS'!K39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Current portion of long-term debt</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G28" s="50">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="50">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="50">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="50">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="50">
+        <f>J28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>Total current liabilities</t>
+        </is>
+      </c>
+      <c r="E29" s="46">
+        <f>SUM(E23:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="46">
+        <f>SUM(F23:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="46">
+        <f>SUM(G23:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="46">
+        <f>SUM(H23:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="46">
+        <f>SUM(I23:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="46">
+        <f>SUM(J23:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="46">
+        <f>SUM(K23:K28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Deferred revenue, non-current</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="n">
+        <v>3031</v>
+      </c>
+      <c r="F30" s="44" t="n">
+        <v>3624</v>
+      </c>
+      <c r="G30" s="50">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="50">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="50">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="50">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="50">
+        <f>J30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>Long-term debt</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>28987</v>
+      </c>
+      <c r="F31" s="44" t="n">
+        <v>53463</v>
+      </c>
+      <c r="G31" s="50">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="50">
+        <f>G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="50">
+        <f>H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="50">
+        <f>I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="50">
+        <f>J31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Other non-current liabilities</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="n">
+        <v>24826</v>
+      </c>
+      <c r="F32" s="44" t="n">
+        <v>33427</v>
+      </c>
+      <c r="G32" s="50">
+        <f>F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="50">
+        <f>G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="50">
+        <f>H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="50">
+        <f>I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="50">
+        <f>J32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="E33" s="46">
+        <f>E29+SUM(E30:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="46">
+        <f>F29+SUM(F30:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="46">
+        <f>G29+SUM(G30:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="46">
+        <f>H29+SUM(H30:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="46">
+        <f>I29+SUM(I30:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="46">
+        <f>J29+SUM(J30:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="46">
+        <f>K29+SUM(K30:K32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Shareholders' equity</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>Common stock and additional paid-in capital</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="n">
+        <v>23313</v>
+      </c>
+      <c r="F36" s="44" t="n">
+        <v>27416</v>
+      </c>
+      <c r="G36" s="50">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="50">
+        <f>G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="50">
+        <f>H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="50">
+        <f>I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="50">
+        <f>J36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="n">
+        <v>87152</v>
+      </c>
+      <c r="F37" s="44" t="n">
+        <v>92284</v>
+      </c>
+      <c r="G37" s="45">
+        <f>F37+'IS'!G26+'CFS'!G37+'CFS'!G38</f>
+        <v/>
+      </c>
+      <c r="H37" s="45">
+        <f>G37+'IS'!H26+'CFS'!H37+'CFS'!H38</f>
+        <v/>
+      </c>
+      <c r="I37" s="45">
+        <f>H37+'IS'!I26+'CFS'!I37+'CFS'!I38</f>
+        <v/>
+      </c>
+      <c r="J37" s="45">
+        <f>I37+'IS'!J26+'CFS'!J37+'CFS'!J38</f>
+        <v/>
+      </c>
+      <c r="K37" s="45">
+        <f>J37+'IS'!K26+'CFS'!K37+'CFS'!K38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>Accumulated other comprehensive income</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="n">
+        <v>1082</v>
+      </c>
+      <c r="F38" s="44" t="n">
+        <v>-345</v>
+      </c>
+      <c r="G38" s="50">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="50">
+        <f>G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="50">
+        <f>H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="50">
+        <f>I38</f>
+        <v/>
+      </c>
+      <c r="K38" s="50">
+        <f>J38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Treasury stock and other equity</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="50">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H39" s="50">
+        <f>G39</f>
+        <v/>
+      </c>
+      <c r="I39" s="50">
+        <f>H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="50">
+        <f>I39</f>
+        <v/>
+      </c>
+      <c r="K39" s="50">
+        <f>J39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>Noncontrolling interests</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="50">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="50">
+        <f>G40</f>
+        <v/>
+      </c>
+      <c r="I40" s="50">
+        <f>H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="50">
+        <f>I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="50">
+        <f>J40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="E41" s="46">
+        <f>SUM(E36:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="46">
+        <f>SUM(F36:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="46">
+        <f>SUM(G36:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="46">
+        <f>SUM(H36:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="46">
+        <f>SUM(I36:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="46">
+        <f>SUM(J36:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="46">
+        <f>SUM(K36:K40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Total liabilities and shareholders' equity</t>
+        </is>
+      </c>
+      <c r="E42" s="51">
+        <f>E33+E41</f>
+        <v/>
+      </c>
+      <c r="F42" s="51">
+        <f>F33+F41</f>
+        <v/>
+      </c>
+      <c r="G42" s="51">
+        <f>G33+G41</f>
+        <v/>
+      </c>
+      <c r="H42" s="51">
+        <f>H33+H41</f>
+        <v/>
+      </c>
+      <c r="I42" s="51">
+        <f>I33+I41</f>
+        <v/>
+      </c>
+      <c r="J42" s="51">
+        <f>J33+J41</f>
+        <v/>
+      </c>
+      <c r="K42" s="51">
+        <f>K33+K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="55" t="inlineStr">
+        <is>
+          <t>Check: Assets - (Liabilities + Equity)</t>
+        </is>
+      </c>
+      <c r="E43" s="56">
+        <f>E20-E42</f>
+        <v/>
+      </c>
+      <c r="F43" s="56">
+        <f>F20-F42</f>
+        <v/>
+      </c>
+      <c r="G43" s="56">
+        <f>G20-G42</f>
+        <v/>
+      </c>
+      <c r="H43" s="56">
+        <f>H20-H42</f>
+        <v/>
+      </c>
+      <c r="I43" s="56">
+        <f>I20-I42</f>
+        <v/>
+      </c>
+      <c r="J43" s="56">
+        <f>J20-J42</f>
+        <v/>
+      </c>
+      <c r="K43" s="56">
+        <f>K20-K42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="23" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Net working capital (operating)</t>
+        </is>
+      </c>
+      <c r="E46" s="50">
+        <f>(E14-E7-E8-E11)-(E29-E26-E27-E28)</f>
+        <v/>
+      </c>
+      <c r="F46" s="50">
+        <f>(F14-F7-F8-F11)-(F29-F26-F27-F28)</f>
+        <v/>
+      </c>
+      <c r="G46" s="50">
+        <f>(G14-G7-G8-G11)-(G29-G26-G27-G28)</f>
+        <v/>
+      </c>
+      <c r="H46" s="50">
+        <f>(H14-H7-H8-H11)-(H29-H26-H27-H28)</f>
+        <v/>
+      </c>
+      <c r="I46" s="50">
+        <f>(I14-I7-I8-I11)-(I29-I26-I27-I28)</f>
+        <v/>
+      </c>
+      <c r="J46" s="50">
+        <f>(J14-J7-J8-J11)-(J29-J26-J27-J28)</f>
+        <v/>
+      </c>
+      <c r="K46" s="50">
+        <f>(K14-K7-K8-K11)-(K29-K26-K27-K28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="E47" s="50">
+        <f>E26+E27+E28+E31</f>
+        <v/>
+      </c>
+      <c r="F47" s="50">
+        <f>F26+F27+F28+F31</f>
+        <v/>
+      </c>
+      <c r="G47" s="50">
+        <f>G26+G27+G28+G31</f>
+        <v/>
+      </c>
+      <c r="H47" s="50">
+        <f>H26+H27+H28+H31</f>
+        <v/>
+      </c>
+      <c r="I47" s="50">
+        <f>I26+I27+I28+I31</f>
+        <v/>
+      </c>
+      <c r="J47" s="50">
+        <f>J26+J27+J28+J31</f>
+        <v/>
+      </c>
+      <c r="K47" s="50">
+        <f>K26+K27+K28+K31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Cash and marketable securities</t>
+        </is>
+      </c>
+      <c r="E48" s="50">
+        <f>E7+E8+E15</f>
+        <v/>
+      </c>
+      <c r="F48" s="50">
+        <f>F7+F8+F15</f>
+        <v/>
+      </c>
+      <c r="G48" s="50">
+        <f>G7+G8+G15</f>
+        <v/>
+      </c>
+      <c r="H48" s="50">
+        <f>H7+H8+H15</f>
+        <v/>
+      </c>
+      <c r="I48" s="50">
+        <f>I7+I8+I15</f>
+        <v/>
+      </c>
+      <c r="J48" s="50">
+        <f>J7+J8+J15</f>
+        <v/>
+      </c>
+      <c r="K48" s="50">
+        <f>K7+K8+K15</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:K50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="14" t="inlineStr">
+        <is>
           <t>Apple Inc.: Cash Flow Statement</t>
         </is>
       </c>
@@ -5798,23 +5990,23 @@
         <v>53394</v>
       </c>
       <c r="G9" s="45">
-        <f>'IS'!G24</f>
+        <f>'IS'!G26</f>
         <v/>
       </c>
       <c r="H9" s="45">
-        <f>'IS'!H24</f>
+        <f>'IS'!H26</f>
         <v/>
       </c>
       <c r="I9" s="45">
-        <f>'IS'!I24</f>
+        <f>'IS'!I26</f>
         <v/>
       </c>
       <c r="J9" s="45">
-        <f>'IS'!J24</f>
+        <f>'IS'!J26</f>
         <v/>
       </c>
       <c r="K9" s="45">
-        <f>'IS'!K24</f>
+        <f>'IS'!K26</f>
         <v/>
       </c>
     </row>
@@ -5834,23 +6026,23 @@
         <v>11257</v>
       </c>
       <c r="G10" s="45">
-        <f>'IS'!G16</f>
+        <f>'IS'!G17</f>
         <v/>
       </c>
       <c r="H10" s="45">
-        <f>'IS'!H16</f>
+        <f>'IS'!H17</f>
         <v/>
       </c>
       <c r="I10" s="45">
-        <f>'IS'!I16</f>
+        <f>'IS'!I17</f>
         <v/>
       </c>
       <c r="J10" s="45">
-        <f>'IS'!J16</f>
+        <f>'IS'!J17</f>
         <v/>
       </c>
       <c r="K10" s="45">
-        <f>'IS'!K16</f>
+        <f>'IS'!K17</f>
         <v/>
       </c>
     </row>
@@ -6289,23 +6481,23 @@
         <v>-11247</v>
       </c>
       <c r="G28" s="45">
-        <f>-'IS'!G7*'Inputs'!G35</f>
+        <f>-'IS'!G7*'Inputs'!G36</f>
         <v/>
       </c>
       <c r="H28" s="45">
-        <f>-'IS'!H7*'Inputs'!H35</f>
+        <f>-'IS'!H7*'Inputs'!H36</f>
         <v/>
       </c>
       <c r="I28" s="45">
-        <f>-'IS'!I7*'Inputs'!I35</f>
+        <f>-'IS'!I7*'Inputs'!I36</f>
         <v/>
       </c>
       <c r="J28" s="45">
-        <f>-'IS'!J7*'Inputs'!J35</f>
+        <f>-'IS'!J7*'Inputs'!J36</f>
         <v/>
       </c>
       <c r="K28" s="45">
-        <f>-'IS'!K7*'Inputs'!K35</f>
+        <f>-'IS'!K7*'Inputs'!K36</f>
         <v/>
       </c>
     </row>
@@ -6460,23 +6652,23 @@
         <v>-11561</v>
       </c>
       <c r="G37" s="45">
-        <f>-'IS'!G24*'Inputs'!G46</f>
+        <f>-MIN(MAX('IS'!G26,0)*'Inputs'!G47,MAX(G6+G21+G31,0))</f>
         <v/>
       </c>
       <c r="H37" s="45">
-        <f>-'IS'!H24*'Inputs'!H46</f>
+        <f>-MIN(MAX('IS'!H26,0)*'Inputs'!H47,MAX(H6+H21+H31,0))</f>
         <v/>
       </c>
       <c r="I37" s="45">
-        <f>-'IS'!I24*'Inputs'!I46</f>
+        <f>-MIN(MAX('IS'!I26,0)*'Inputs'!I47,MAX(I6+I21+I31,0))</f>
         <v/>
       </c>
       <c r="J37" s="45">
-        <f>-'IS'!J24*'Inputs'!J46</f>
+        <f>-MIN(MAX('IS'!J26,0)*'Inputs'!J47,MAX(J6+J21+J31,0))</f>
         <v/>
       </c>
       <c r="K37" s="45">
-        <f>-'IS'!K24*'Inputs'!K46</f>
+        <f>-MIN(MAX('IS'!K26,0)*'Inputs'!K47,MAX(K6+K21+K31,0))</f>
         <v/>
       </c>
     </row>
@@ -6496,30 +6688,30 @@
         <v>-35253</v>
       </c>
       <c r="G38" s="45">
-        <f>-'IS'!G24*'Inputs'!G47</f>
+        <f>-MIN(MAX('IS'!G26,0)*'Inputs'!G48,MAX(MAX(G6+G21+G31,0)+G37,0))</f>
         <v/>
       </c>
       <c r="H38" s="45">
-        <f>-'IS'!H24*'Inputs'!H47</f>
+        <f>-MIN(MAX('IS'!H26,0)*'Inputs'!H48,MAX(MAX(H6+H21+H31,0)+H37,0))</f>
         <v/>
       </c>
       <c r="I38" s="45">
-        <f>-'IS'!I24*'Inputs'!I47</f>
+        <f>-MIN(MAX('IS'!I26,0)*'Inputs'!I48,MAX(MAX(I6+I21+I31,0)+I37,0))</f>
         <v/>
       </c>
       <c r="J38" s="45">
-        <f>-'IS'!J24*'Inputs'!J47</f>
+        <f>-MIN(MAX('IS'!J26,0)*'Inputs'!J48,MAX(MAX(J6+J21+J31,0)+J37,0))</f>
         <v/>
       </c>
       <c r="K38" s="45">
-        <f>-'IS'!K24*'Inputs'!K47</f>
+        <f>-MIN(MAX('IS'!K26,0)*'Inputs'!K48,MAX(MAX(K6+K21+K31,0)+K37,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of debt, net</t>
+          <t>Proceeds from debt (projection: revolver draw)</t>
         </is>
       </c>
       <c r="D39" s="44" t="n">
@@ -6531,6 +6723,26 @@
       <c r="F39" s="44" t="n">
         <v>27114</v>
       </c>
+      <c r="G39" s="50">
+        <f>MAX(-(G6+G21+G31),0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="50">
+        <f>MAX(-(H6+H21+H31),0)</f>
+        <v/>
+      </c>
+      <c r="I39" s="50">
+        <f>MAX(-(I6+I21+I31),0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="50">
+        <f>MAX(-(J6+J21+J31),0)</f>
+        <v/>
+      </c>
+      <c r="K39" s="50">
+        <f>MAX(-(K6+K21+K31),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="24" t="inlineStr">
@@ -6620,134 +6832,166 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="41" t="inlineStr">
-        <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D45" s="46">
-        <f>D21+D31+D43</f>
-        <v/>
-      </c>
-      <c r="E45" s="46">
-        <f>E21+E31+E43</f>
-        <v/>
-      </c>
-      <c r="F45" s="46">
-        <f>F21+F31+F43</f>
-        <v/>
-      </c>
-      <c r="G45" s="46">
-        <f>G21+G31+G43</f>
-        <v/>
-      </c>
-      <c r="H45" s="46">
-        <f>H21+H31+H43</f>
-        <v/>
-      </c>
-      <c r="I45" s="46">
-        <f>I21+I31+I43</f>
-        <v/>
-      </c>
-      <c r="J45" s="46">
-        <f>J21+J31+J43</f>
-        <v/>
-      </c>
-      <c r="K45" s="46">
-        <f>K21+K31+K43</f>
-        <v/>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Exchange-rate effect and other</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="41" t="inlineStr">
         <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D46" s="46">
+        <f>D21+D31+D43+D45</f>
+        <v/>
+      </c>
+      <c r="E46" s="46">
+        <f>E21+E31+E43+E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="46">
+        <f>F21+F31+F43+F45</f>
+        <v/>
+      </c>
+      <c r="G46" s="46">
+        <f>G21+G31+G43+G45</f>
+        <v/>
+      </c>
+      <c r="H46" s="46">
+        <f>H21+H31+H43+H45</f>
+        <v/>
+      </c>
+      <c r="I46" s="46">
+        <f>I21+I31+I43+I45</f>
+        <v/>
+      </c>
+      <c r="J46" s="46">
+        <f>J21+J31+J43+J45</f>
+        <v/>
+      </c>
+      <c r="K46" s="46">
+        <f>K21+K31+K43+K45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="41" t="inlineStr">
+        <is>
           <t>Cash, end of year</t>
         </is>
       </c>
-      <c r="D46" s="51">
-        <f>D6+D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="51">
-        <f>E6+E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="51">
-        <f>F6+F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="51">
-        <f>G6+G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="51">
-        <f>H6+H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="51">
-        <f>I6+I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="51">
-        <f>J6+J45</f>
-        <v/>
-      </c>
-      <c r="K46" s="51">
-        <f>K6+K45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="55" t="inlineStr">
-        <is>
-          <t>Check: ending cash - balance sheet cash</t>
-        </is>
-      </c>
-      <c r="E47" s="56">
-        <f>E46-'BS'!E7</f>
-        <v/>
-      </c>
-      <c r="F47" s="56">
-        <f>F46-'BS'!F7</f>
-        <v/>
-      </c>
-      <c r="G47" s="56">
-        <f>G46-'BS'!G7</f>
-        <v/>
-      </c>
-      <c r="H47" s="56">
-        <f>H46-'BS'!H7</f>
-        <v/>
-      </c>
-      <c r="I47" s="56">
-        <f>I46-'BS'!I7</f>
-        <v/>
-      </c>
-      <c r="J47" s="56">
-        <f>J46-'BS'!J7</f>
-        <v/>
-      </c>
-      <c r="K47" s="56">
-        <f>K46-'BS'!K7</f>
+      <c r="D47" s="51">
+        <f>D6+D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="51">
+        <f>E6+E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="51">
+        <f>F6+F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="51">
+        <f>G6+G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="51">
+        <f>H6+H46</f>
+        <v/>
+      </c>
+      <c r="I47" s="51">
+        <f>I6+I46</f>
+        <v/>
+      </c>
+      <c r="J47" s="51">
+        <f>J6+J46</f>
+        <v/>
+      </c>
+      <c r="K47" s="51">
+        <f>K6+K46</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="55" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which restricted cash (not in balance sheet cash)</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="55" t="inlineStr">
+        <is>
+          <t>Check: ending cash ex. restricted - balance sheet cash</t>
+        </is>
+      </c>
+      <c r="E49" s="56">
+        <f>E47-E48-'BS'!E7</f>
+        <v/>
+      </c>
+      <c r="F49" s="56">
+        <f>F47-F48-'BS'!F7</f>
+        <v/>
+      </c>
+      <c r="G49" s="56">
+        <f>G47-G48-'BS'!G7</f>
+        <v/>
+      </c>
+      <c r="H49" s="56">
+        <f>H47-H48-'BS'!H7</f>
+        <v/>
+      </c>
+      <c r="I49" s="56">
+        <f>I47-I48-'BS'!I7</f>
+        <v/>
+      </c>
+      <c r="J49" s="56">
+        <f>J47-J48-'BS'!J7</f>
+        <v/>
+      </c>
+      <c r="K49" s="56">
+        <f>K47-K48-'BS'!K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>Check: CFS net income - IS net income</t>
         </is>
       </c>
-      <c r="D48" s="56">
-        <f>D9-'IS'!D24</f>
-        <v/>
-      </c>
-      <c r="E48" s="56">
-        <f>E9-'IS'!E24</f>
-        <v/>
-      </c>
-      <c r="F48" s="56">
-        <f>F9-'IS'!F24</f>
+      <c r="D50" s="56">
+        <f>D9-'IS'!D26</f>
+        <v/>
+      </c>
+      <c r="E50" s="56">
+        <f>E9-'IS'!E26</f>
+        <v/>
+      </c>
+      <c r="F50" s="56">
+        <f>F9-'IS'!F26</f>
         <v/>
       </c>
     </row>
@@ -7796,7 +8040,7 @@
         </is>
       </c>
       <c r="D43" s="45">
-        <f>'BS'!F27+'BS'!F30</f>
+        <f>'BS'!F28+'BS'!F31</f>
         <v/>
       </c>
     </row>
@@ -7866,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K52"/>
+  <dimension ref="B1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7997,7 +8241,7 @@
         </is>
       </c>
       <c r="D10" s="45">
-        <f>'BS'!F44</f>
+        <f>'BS'!F47</f>
         <v/>
       </c>
     </row>
@@ -8085,7 +8329,7 @@
         </is>
       </c>
       <c r="D18" s="40">
-        <f>'Inputs'!$G$45</f>
+        <f>'Inputs'!$G$46</f>
         <v/>
       </c>
     </row>
@@ -8145,23 +8389,23 @@
         </is>
       </c>
       <c r="G24" s="45">
-        <f>'IS'!G14</f>
+        <f>'IS'!G15</f>
         <v/>
       </c>
       <c r="H24" s="45">
-        <f>'IS'!H14</f>
+        <f>'IS'!H15</f>
         <v/>
       </c>
       <c r="I24" s="45">
-        <f>'IS'!I14</f>
+        <f>'IS'!I15</f>
         <v/>
       </c>
       <c r="J24" s="45">
-        <f>'IS'!J14</f>
+        <f>'IS'!J15</f>
         <v/>
       </c>
       <c r="K24" s="45">
-        <f>'IS'!K14</f>
+        <f>'IS'!K15</f>
         <v/>
       </c>
     </row>
@@ -8172,23 +8416,23 @@
         </is>
       </c>
       <c r="G25" s="36">
-        <f>'Inputs'!G36</f>
+        <f>'Inputs'!G37</f>
         <v/>
       </c>
       <c r="H25" s="36">
-        <f>'Inputs'!H36</f>
+        <f>'Inputs'!H37</f>
         <v/>
       </c>
       <c r="I25" s="36">
-        <f>'Inputs'!I36</f>
+        <f>'Inputs'!I37</f>
         <v/>
       </c>
       <c r="J25" s="36">
-        <f>'Inputs'!J36</f>
+        <f>'Inputs'!J37</f>
         <v/>
       </c>
       <c r="K25" s="36">
-        <f>'Inputs'!K36</f>
+        <f>'Inputs'!K37</f>
         <v/>
       </c>
     </row>
@@ -8226,23 +8470,23 @@
         </is>
       </c>
       <c r="G27" s="45">
-        <f>'IS'!G16</f>
+        <f>'IS'!G17</f>
         <v/>
       </c>
       <c r="H27" s="45">
-        <f>'IS'!H16</f>
+        <f>'IS'!H17</f>
         <v/>
       </c>
       <c r="I27" s="45">
-        <f>'IS'!I16</f>
+        <f>'IS'!I17</f>
         <v/>
       </c>
       <c r="J27" s="45">
-        <f>'IS'!J16</f>
+        <f>'IS'!J17</f>
         <v/>
       </c>
       <c r="K27" s="45">
-        <f>'IS'!K16</f>
+        <f>'IS'!K17</f>
         <v/>
       </c>
     </row>
@@ -8280,23 +8524,23 @@
         </is>
       </c>
       <c r="G29" s="45">
-        <f>'BS'!G43-'BS'!F43</f>
+        <f>'BS'!G46-'BS'!F46</f>
         <v/>
       </c>
       <c r="H29" s="45">
-        <f>'BS'!H43-'BS'!G43</f>
+        <f>'BS'!H46-'BS'!G46</f>
         <v/>
       </c>
       <c r="I29" s="45">
-        <f>'BS'!I43-'BS'!H43</f>
+        <f>'BS'!I46-'BS'!H46</f>
         <v/>
       </c>
       <c r="J29" s="45">
-        <f>'BS'!J43-'BS'!I43</f>
+        <f>'BS'!J46-'BS'!I46</f>
         <v/>
       </c>
       <c r="K29" s="45">
-        <f>'BS'!K43-'BS'!J43</f>
+        <f>'BS'!K46-'BS'!J46</f>
         <v/>
       </c>
     </row>
@@ -8500,7 +8744,7 @@
         <v/>
       </c>
       <c r="E39" s="45">
-        <f>'IS'!K17</f>
+        <f>'IS'!K18</f>
         <v/>
       </c>
     </row>
@@ -8571,11 +8815,11 @@
         </is>
       </c>
       <c r="D44" s="45">
-        <f>'BS'!F45</f>
+        <f>'BS'!F48</f>
         <v/>
       </c>
       <c r="E44" s="45">
-        <f>'BS'!F45</f>
+        <f>'BS'!F48</f>
         <v/>
       </c>
     </row>
@@ -8597,104 +8841,119 @@
     <row r="46">
       <c r="B46" s="24" t="inlineStr">
         <is>
+          <t>Less: noncontrolling interests</t>
+        </is>
+      </c>
+      <c r="D46" s="45">
+        <f>-'BS'!F40</f>
+        <v/>
+      </c>
+      <c r="E46" s="45">
+        <f>-'BS'!F40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="24" t="inlineStr">
+        <is>
           <t>Less: repatriation tax on offshore cash</t>
         </is>
       </c>
-      <c r="D46" s="45">
+      <c r="D47" s="45">
         <f>-IF('Inputs'!$D$15=1,'Inputs'!$D$24*'Inputs'!$D$16,0)</f>
         <v/>
       </c>
-      <c r="E46" s="45">
+      <c r="E47" s="45">
         <f>-IF('Inputs'!$D$15=1,'Inputs'!$D$24*'Inputs'!$D$16,0)</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="41" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>Implied equity value</t>
         </is>
       </c>
-      <c r="D47" s="46">
-        <f>SUM(D43:D46)</f>
-        <v/>
-      </c>
-      <c r="E47" s="46">
-        <f>SUM(E43:E46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="24" t="inlineStr">
+      <c r="D48" s="46">
+        <f>SUM(D43:D47)</f>
+        <v/>
+      </c>
+      <c r="E48" s="46">
+        <f>SUM(E43:E47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>Diluted shares (m)</t>
         </is>
       </c>
-      <c r="D48" s="34">
+      <c r="D49" s="34">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="E48" s="34">
+      <c r="E49" s="34">
         <f>$D$8</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="41" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="D49" s="68">
-        <f>D47/D48</f>
-        <v/>
-      </c>
-      <c r="E49" s="68">
-        <f>E47/E48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Premium / (discount) to current price</t>
-        </is>
-      </c>
-      <c r="D50" s="31">
-        <f>D49/$D$7-1</f>
-        <v/>
-      </c>
-      <c r="E50" s="31">
-        <f>E49/$D$7-1</f>
+      <c r="D50" s="68">
+        <f>D48/D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="68">
+        <f>E48/E49</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>PV of terminal value, % of EV</t>
+          <t>Premium / (discount) to current price</t>
         </is>
       </c>
       <c r="D51" s="31">
-        <f>D42/D43</f>
+        <f>D50/$D$7-1</f>
         <v/>
       </c>
       <c r="E51" s="31">
-        <f>E42/E43</f>
+        <f>E50/$D$7-1</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="24" t="inlineStr">
         <is>
+          <t>PV of terminal value, % of EV</t>
+        </is>
+      </c>
+      <c r="D52" s="31">
+        <f>D42/D43</f>
+        <v/>
+      </c>
+      <c r="E52" s="31">
+        <f>E42/E43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="24" t="inlineStr">
+        <is>
           <t>Implied exit multiple / implied perpetual growth</t>
         </is>
       </c>
-      <c r="D52" s="69">
+      <c r="D53" s="69">
         <f>D40/E39</f>
         <v/>
       </c>
-      <c r="E52" s="31">
+      <c r="E53" s="31">
         <f>(E40*$D$21-D39)/(E40+D39)</f>
         <v/>
       </c>
@@ -8715,7 +8974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:K101"/>
+  <dimension ref="B1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8813,7 +9072,7 @@
         </is>
       </c>
       <c r="D7" s="45">
-        <f>'IS'!F17</f>
+        <f>'IS'!F18</f>
         <v/>
       </c>
     </row>
@@ -8824,7 +9083,7 @@
         </is>
       </c>
       <c r="D8" s="67">
-        <f>'Inputs'!$D$50</f>
+        <f>'Inputs'!$D$51</f>
         <v/>
       </c>
     </row>
@@ -8846,1566 +9105,1588 @@
         </is>
       </c>
       <c r="D10" s="45">
-        <f>'BS'!F44</f>
+        <f>'BS'!F47</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="24" t="inlineStr">
         <is>
+          <t>Less: noncontrolling interests (not acquired)</t>
+        </is>
+      </c>
+      <c r="D11" s="45">
+        <f>'BS'!F40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
           <t>Plus: cash &amp; marketable securities</t>
         </is>
       </c>
-      <c r="D11" s="45">
-        <f>'BS'!F45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="41" t="inlineStr">
+      <c r="D12" s="45">
+        <f>'BS'!F48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Equity purchase price</t>
         </is>
       </c>
-      <c r="D12" s="46">
-        <f>$D$9-$D$10+$D$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Diluted shares (m)</t>
-        </is>
-      </c>
-      <c r="D13" s="53">
-        <f>'Inputs'!$D$23</f>
+      <c r="D13" s="46">
+        <f>$D$9-$D$10-$D$11+$D$12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Implied offer price per share</t>
-        </is>
-      </c>
-      <c r="D14" s="54">
-        <f>$D$12/$D$13</f>
+          <t>Diluted shares (m)</t>
+        </is>
+      </c>
+      <c r="D14" s="53">
+        <f>'Inputs'!$D$23</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="24" t="inlineStr">
         <is>
+          <t>Implied offer price per share</t>
+        </is>
+      </c>
+      <c r="D15" s="54">
+        <f>$D$13/$D$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
           <t>Premium to current share price</t>
         </is>
       </c>
-      <c r="D15" s="36">
-        <f>$D$14/'Inputs'!$D$7-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="D16" s="36">
+        <f>$D$15/'Inputs'!$D$7-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Cash available at close</t>
         </is>
       </c>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="n"/>
-      <c r="G17" s="23" t="n"/>
-      <c r="H17" s="23" t="n"/>
-      <c r="I17" s="23" t="n"/>
-      <c r="J17" s="23" t="n"/>
-      <c r="K17" s="23" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Offshore cash &amp; securities</t>
-        </is>
-      </c>
-      <c r="D18" s="45">
-        <f>'Inputs'!$D$24</f>
-        <v/>
-      </c>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Domestic cash &amp; securities</t>
-        </is>
-      </c>
-      <c r="D19" s="50">
-        <f>$D$11-$D$18</f>
+          <t>Offshore cash &amp; securities</t>
+        </is>
+      </c>
+      <c r="D19" s="45">
+        <f>'Inputs'!$D$24</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Minimum operating cash</t>
-        </is>
-      </c>
-      <c r="D20" s="45">
-        <f>'Inputs'!$D$55</f>
+          <t>Domestic cash &amp; securities</t>
+        </is>
+      </c>
+      <c r="D20" s="50">
+        <f>$D$12-$D$19</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Domestic cash used to fund the deal</t>
-        </is>
-      </c>
-      <c r="D21" s="50">
-        <f>MAX($D$19-$D$20,0)</f>
+          <t>Minimum operating cash</t>
+        </is>
+      </c>
+      <c r="D21" s="45">
+        <f>'Inputs'!$D$56</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Cash retained on balance sheet</t>
+          <t>Domestic cash used to fund the deal</t>
         </is>
       </c>
       <c r="D22" s="50">
-        <f>$D$19-$D$21</f>
+        <f>MAX($D$20-$D$21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Offshore cash repatriated</t>
-        </is>
-      </c>
-      <c r="D23" s="45">
-        <f>$D$18*'Inputs'!$D$58</f>
+          <t>Cash retained on balance sheet</t>
+        </is>
+      </c>
+      <c r="D23" s="50">
+        <f>$D$20-$D$22</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Repatriation tax paid</t>
+          <t>Offshore cash repatriated</t>
         </is>
       </c>
       <c r="D24" s="45">
-        <f>$D$23*'Inputs'!$D$16</f>
+        <f>$D$19*'Inputs'!$D$59</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="24" t="inlineStr">
         <is>
+          <t>Repatriation tax paid</t>
+        </is>
+      </c>
+      <c r="D25" s="45">
+        <f>$D$24*'Inputs'!$D$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
           <t>Offshore cash remaining trapped</t>
         </is>
       </c>
-      <c r="D25" s="50">
-        <f>$D$18-$D$23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="23" t="inlineStr">
+      <c r="D26" s="50">
+        <f>$D$19-$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Uses of funds</t>
         </is>
       </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="23" t="n"/>
-      <c r="H27" s="23" t="n"/>
-      <c r="I27" s="23" t="n"/>
-      <c r="J27" s="23" t="n"/>
-      <c r="K27" s="23" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Purchase of equity</t>
-        </is>
-      </c>
-      <c r="D28" s="50">
-        <f>$D$12</f>
-        <v/>
-      </c>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Refinance existing debt</t>
+          <t>Purchase of equity</t>
         </is>
       </c>
       <c r="D29" s="50">
-        <f>$D$10</f>
+        <f>$D$13</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Advisory &amp; transaction fees</t>
-        </is>
-      </c>
-      <c r="D30" s="45">
-        <f>$D$9*'Inputs'!$D$56</f>
+          <t>Refinance existing debt</t>
+        </is>
+      </c>
+      <c r="D30" s="50">
+        <f>$D$10</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="24" t="inlineStr">
         <is>
+          <t>Advisory &amp; transaction fees</t>
+        </is>
+      </c>
+      <c r="D31" s="45">
+        <f>$D$9*'Inputs'!$D$57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
           <t>Financing fees</t>
         </is>
       </c>
-      <c r="D31" s="45">
-        <f>$D$35*'Inputs'!$D$57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="41" t="inlineStr">
+      <c r="D32" s="45">
+        <f>$D$36*'Inputs'!$D$58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>Total uses</t>
         </is>
       </c>
-      <c r="D32" s="51">
-        <f>SUM(D28:D31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="23" t="inlineStr">
+      <c r="D33" s="51">
+        <f>SUM(D29:D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Sources of funds</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="23" t="n"/>
-      <c r="H34" s="23" t="n"/>
-      <c r="I34" s="23" t="n"/>
-      <c r="J34" s="23" t="n"/>
-      <c r="K34" s="23" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Total new debt</t>
-        </is>
-      </c>
-      <c r="D35" s="45">
-        <f>$D$9*'Inputs'!$D$53</f>
-        <v/>
-      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Senior Term Loan B</t>
+          <t>Total new debt</t>
         </is>
       </c>
       <c r="D36" s="45">
-        <f>$D$35*'Inputs'!$D$63</f>
+        <f>$D$9*'Inputs'!$D$54</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Senior Subordinated Notes</t>
+          <t xml:space="preserve">  Senior Term Loan B</t>
         </is>
       </c>
       <c r="D37" s="45">
-        <f>$D$35*'Inputs'!$D$69</f>
+        <f>$D$36*'Inputs'!$D$64</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="24" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Senior Subordinated Notes</t>
+        </is>
+      </c>
+      <c r="D38" s="45">
+        <f>$D$36*'Inputs'!$D$70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="24" t="inlineStr">
+        <is>
           <t>Existing cash &amp; securities used</t>
         </is>
       </c>
-      <c r="D38" s="50">
-        <f>$D$21+$D$23-$D$24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="41" t="inlineStr">
-        <is>
-          <t>Sponsor equity</t>
-        </is>
-      </c>
-      <c r="D39" s="46">
-        <f>$D$32-$D$35-$D$38</f>
+      <c r="D39" s="50">
+        <f>$D$22+$D$24-$D$25</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="41" t="inlineStr">
         <is>
+          <t>Sponsor equity</t>
+        </is>
+      </c>
+      <c r="D40" s="46">
+        <f>$D$33-$D$36-$D$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="41" t="inlineStr">
+        <is>
           <t>Total sources</t>
         </is>
       </c>
-      <c r="D40" s="51">
-        <f>SUM(D36:D39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="55" t="inlineStr">
+      <c r="D41" s="51">
+        <f>SUM(D37:D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>Check: sources - uses</t>
         </is>
       </c>
-      <c r="D41" s="56">
-        <f>$D$40-$D$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="24" t="inlineStr">
+      <c r="D42" s="56">
+        <f>$D$41-$D$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="24" t="inlineStr">
         <is>
           <t>Total debt / LTM EBITDA</t>
         </is>
       </c>
-      <c r="D42" s="69">
-        <f>$D$35/$D$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="23" t="inlineStr">
+      <c r="D43" s="69">
+        <f>$D$36/$D$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>Cash flow available for debt service</t>
         </is>
       </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="23" t="n"/>
-      <c r="G44" s="23" t="n"/>
-      <c r="H44" s="23" t="n"/>
-      <c r="I44" s="23" t="n"/>
-      <c r="J44" s="23" t="n"/>
-      <c r="K44" s="23" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="G45" s="45">
-        <f>'IS'!G17</f>
-        <v/>
-      </c>
-      <c r="H45" s="45">
-        <f>'IS'!H17</f>
-        <v/>
-      </c>
-      <c r="I45" s="45">
-        <f>'IS'!I17</f>
-        <v/>
-      </c>
-      <c r="J45" s="45">
-        <f>'IS'!J17</f>
-        <v/>
-      </c>
-      <c r="K45" s="45">
-        <f>'IS'!K17</f>
-        <v/>
-      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="23" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>Less: D&amp;A</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="G46" s="45">
-        <f>'IS'!G16</f>
+        <f>'IS'!G18</f>
         <v/>
       </c>
       <c r="H46" s="45">
-        <f>'IS'!H16</f>
+        <f>'IS'!H18</f>
         <v/>
       </c>
       <c r="I46" s="45">
-        <f>'IS'!I16</f>
+        <f>'IS'!I18</f>
         <v/>
       </c>
       <c r="J46" s="45">
-        <f>'IS'!J16</f>
+        <f>'IS'!J18</f>
         <v/>
       </c>
       <c r="K46" s="45">
-        <f>'IS'!K16</f>
+        <f>'IS'!K18</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="G47" s="50">
-        <f>G45-G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="50">
-        <f>H45-H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="50">
-        <f>I45-I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="50">
-        <f>J45-J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="50">
-        <f>K45-K46</f>
+          <t>Less: D&amp;A</t>
+        </is>
+      </c>
+      <c r="G47" s="45">
+        <f>'IS'!G17</f>
+        <v/>
+      </c>
+      <c r="H47" s="45">
+        <f>'IS'!H17</f>
+        <v/>
+      </c>
+      <c r="I47" s="45">
+        <f>'IS'!I17</f>
+        <v/>
+      </c>
+      <c r="J47" s="45">
+        <f>'IS'!J17</f>
+        <v/>
+      </c>
+      <c r="K47" s="45">
+        <f>'IS'!K17</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>Plus: interest income on cash</t>
-        </is>
-      </c>
-      <c r="G48" s="45">
-        <f>'Inputs'!G44*G61</f>
-        <v/>
-      </c>
-      <c r="H48" s="45">
-        <f>'Inputs'!H44*H61</f>
-        <v/>
-      </c>
-      <c r="I48" s="45">
-        <f>'Inputs'!I44*I61</f>
-        <v/>
-      </c>
-      <c r="J48" s="45">
-        <f>'Inputs'!J44*J61</f>
-        <v/>
-      </c>
-      <c r="K48" s="45">
-        <f>'Inputs'!K44*K61</f>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="G48" s="50">
+        <f>G46-G47</f>
+        <v/>
+      </c>
+      <c r="H48" s="50">
+        <f>H46-H47</f>
+        <v/>
+      </c>
+      <c r="I48" s="50">
+        <f>I46-I47</f>
+        <v/>
+      </c>
+      <c r="J48" s="50">
+        <f>J46-J47</f>
+        <v/>
+      </c>
+      <c r="K48" s="50">
+        <f>K46-K47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>Less: interest, Senior Term Loan B</t>
+          <t>Plus: interest income on cash</t>
         </is>
       </c>
       <c r="G49" s="45">
-        <f>'Inputs'!$D$64*G69</f>
+        <f>'Inputs'!G45*G62</f>
         <v/>
       </c>
       <c r="H49" s="45">
-        <f>'Inputs'!$D$64*H69</f>
+        <f>'Inputs'!H45*H62</f>
         <v/>
       </c>
       <c r="I49" s="45">
-        <f>'Inputs'!$D$64*I69</f>
+        <f>'Inputs'!I45*I62</f>
         <v/>
       </c>
       <c r="J49" s="45">
-        <f>'Inputs'!$D$64*J69</f>
+        <f>'Inputs'!J45*J62</f>
         <v/>
       </c>
       <c r="K49" s="45">
-        <f>'Inputs'!$D$64*K69</f>
+        <f>'Inputs'!K45*K62</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="24" t="inlineStr">
         <is>
+          <t>Less: interest, Senior Term Loan B</t>
+        </is>
+      </c>
+      <c r="G50" s="45">
+        <f>'Inputs'!$D$65*G70</f>
+        <v/>
+      </c>
+      <c r="H50" s="45">
+        <f>'Inputs'!$D$65*H70</f>
+        <v/>
+      </c>
+      <c r="I50" s="45">
+        <f>'Inputs'!$D$65*I70</f>
+        <v/>
+      </c>
+      <c r="J50" s="45">
+        <f>'Inputs'!$D$65*J70</f>
+        <v/>
+      </c>
+      <c r="K50" s="45">
+        <f>'Inputs'!$D$65*K70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="24" t="inlineStr">
+        <is>
           <t>Less: interest, Senior Subordinated Notes</t>
         </is>
       </c>
-      <c r="G50" s="45">
-        <f>'Inputs'!$D$70*G75</f>
-        <v/>
-      </c>
-      <c r="H50" s="45">
-        <f>'Inputs'!$D$70*H75</f>
-        <v/>
-      </c>
-      <c r="I50" s="45">
-        <f>'Inputs'!$D$70*I75</f>
-        <v/>
-      </c>
-      <c r="J50" s="45">
-        <f>'Inputs'!$D$70*J75</f>
-        <v/>
-      </c>
-      <c r="K50" s="45">
-        <f>'Inputs'!$D$70*K75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="41" t="inlineStr">
+      <c r="G51" s="45">
+        <f>'Inputs'!$D$71*G76</f>
+        <v/>
+      </c>
+      <c r="H51" s="45">
+        <f>'Inputs'!$D$71*H76</f>
+        <v/>
+      </c>
+      <c r="I51" s="45">
+        <f>'Inputs'!$D$71*I76</f>
+        <v/>
+      </c>
+      <c r="J51" s="45">
+        <f>'Inputs'!$D$71*J76</f>
+        <v/>
+      </c>
+      <c r="K51" s="45">
+        <f>'Inputs'!$D$71*K76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>Total interest expense</t>
         </is>
       </c>
-      <c r="G51" s="46">
-        <f>G49+G50</f>
-        <v/>
-      </c>
-      <c r="H51" s="46">
-        <f>H49+H50</f>
-        <v/>
-      </c>
-      <c r="I51" s="46">
-        <f>I49+I50</f>
-        <v/>
-      </c>
-      <c r="J51" s="46">
-        <f>J49+J50</f>
-        <v/>
-      </c>
-      <c r="K51" s="46">
-        <f>K49+K50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>Pre-tax income</t>
-        </is>
-      </c>
-      <c r="G52" s="50">
-        <f>G47+G48-G51</f>
-        <v/>
-      </c>
-      <c r="H52" s="50">
-        <f>H47+H48-H51</f>
-        <v/>
-      </c>
-      <c r="I52" s="50">
-        <f>I47+I48-I51</f>
-        <v/>
-      </c>
-      <c r="J52" s="50">
-        <f>J47+J48-J51</f>
-        <v/>
-      </c>
-      <c r="K52" s="50">
-        <f>K47+K48-K51</f>
+      <c r="G52" s="46">
+        <f>G50+G51</f>
+        <v/>
+      </c>
+      <c r="H52" s="46">
+        <f>H50+H51</f>
+        <v/>
+      </c>
+      <c r="I52" s="46">
+        <f>I50+I51</f>
+        <v/>
+      </c>
+      <c r="J52" s="46">
+        <f>J50+J51</f>
+        <v/>
+      </c>
+      <c r="K52" s="46">
+        <f>K50+K51</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="G53" s="36">
-        <f>'Inputs'!G36</f>
-        <v/>
-      </c>
-      <c r="H53" s="36">
-        <f>'Inputs'!H36</f>
-        <v/>
-      </c>
-      <c r="I53" s="36">
-        <f>'Inputs'!I36</f>
-        <v/>
-      </c>
-      <c r="J53" s="36">
-        <f>'Inputs'!J36</f>
-        <v/>
-      </c>
-      <c r="K53" s="36">
-        <f>'Inputs'!K36</f>
+          <t>Pre-tax income</t>
+        </is>
+      </c>
+      <c r="G53" s="50">
+        <f>G48+G49-G52</f>
+        <v/>
+      </c>
+      <c r="H53" s="50">
+        <f>H48+H49-H52</f>
+        <v/>
+      </c>
+      <c r="I53" s="50">
+        <f>I48+I49-I52</f>
+        <v/>
+      </c>
+      <c r="J53" s="50">
+        <f>J48+J49-J52</f>
+        <v/>
+      </c>
+      <c r="K53" s="50">
+        <f>K48+K49-K52</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="24" t="inlineStr">
         <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="G54" s="36">
+        <f>'Inputs'!G37</f>
+        <v/>
+      </c>
+      <c r="H54" s="36">
+        <f>'Inputs'!H37</f>
+        <v/>
+      </c>
+      <c r="I54" s="36">
+        <f>'Inputs'!I37</f>
+        <v/>
+      </c>
+      <c r="J54" s="36">
+        <f>'Inputs'!J37</f>
+        <v/>
+      </c>
+      <c r="K54" s="36">
+        <f>'Inputs'!K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="24" t="inlineStr">
+        <is>
           <t>Less: cash taxes (no NOL carry-forward)</t>
         </is>
       </c>
-      <c r="G54" s="50">
-        <f>MAX(G52,0)*G53</f>
-        <v/>
-      </c>
-      <c r="H54" s="50">
-        <f>MAX(H52,0)*H53</f>
-        <v/>
-      </c>
-      <c r="I54" s="50">
-        <f>MAX(I52,0)*I53</f>
-        <v/>
-      </c>
-      <c r="J54" s="50">
-        <f>MAX(J52,0)*J53</f>
-        <v/>
-      </c>
-      <c r="K54" s="50">
-        <f>MAX(K52,0)*K53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="41" t="inlineStr">
+      <c r="G55" s="50">
+        <f>MAX(G53,0)*G54</f>
+        <v/>
+      </c>
+      <c r="H55" s="50">
+        <f>MAX(H53,0)*H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="50">
+        <f>MAX(I53,0)*I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="50">
+        <f>MAX(J53,0)*J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="50">
+        <f>MAX(K53,0)*K54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="G55" s="46">
-        <f>G52-G54</f>
-        <v/>
-      </c>
-      <c r="H55" s="46">
-        <f>H52-H54</f>
-        <v/>
-      </c>
-      <c r="I55" s="46">
-        <f>I52-I54</f>
-        <v/>
-      </c>
-      <c r="J55" s="46">
-        <f>J52-J54</f>
-        <v/>
-      </c>
-      <c r="K55" s="46">
-        <f>K52-K54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>Less: capital expenditures</t>
-        </is>
-      </c>
-      <c r="G56" s="45">
-        <f>-'CFS'!G28</f>
-        <v/>
-      </c>
-      <c r="H56" s="45">
-        <f>-'CFS'!H28</f>
-        <v/>
-      </c>
-      <c r="I56" s="45">
-        <f>-'CFS'!I28</f>
-        <v/>
-      </c>
-      <c r="J56" s="45">
-        <f>-'CFS'!J28</f>
-        <v/>
-      </c>
-      <c r="K56" s="45">
-        <f>-'CFS'!K28</f>
+      <c r="G56" s="46">
+        <f>G53-G55</f>
+        <v/>
+      </c>
+      <c r="H56" s="46">
+        <f>H53-H55</f>
+        <v/>
+      </c>
+      <c r="I56" s="46">
+        <f>I53-I55</f>
+        <v/>
+      </c>
+      <c r="J56" s="46">
+        <f>J53-J55</f>
+        <v/>
+      </c>
+      <c r="K56" s="46">
+        <f>K53-K55</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="24" t="inlineStr">
         <is>
+          <t>Less: capital expenditures</t>
+        </is>
+      </c>
+      <c r="G57" s="45">
+        <f>-'CFS'!G28</f>
+        <v/>
+      </c>
+      <c r="H57" s="45">
+        <f>-'CFS'!H28</f>
+        <v/>
+      </c>
+      <c r="I57" s="45">
+        <f>-'CFS'!I28</f>
+        <v/>
+      </c>
+      <c r="J57" s="45">
+        <f>-'CFS'!J28</f>
+        <v/>
+      </c>
+      <c r="K57" s="45">
+        <f>-'CFS'!K28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="24" t="inlineStr">
+        <is>
           <t>Less: increase in net working capital</t>
         </is>
       </c>
-      <c r="G57" s="45">
+      <c r="G58" s="45">
         <f>'DCF'!G29</f>
         <v/>
       </c>
-      <c r="H57" s="45">
+      <c r="H58" s="45">
         <f>'DCF'!H29</f>
         <v/>
       </c>
-      <c r="I57" s="45">
+      <c r="I58" s="45">
         <f>'DCF'!I29</f>
         <v/>
       </c>
-      <c r="J57" s="45">
+      <c r="J58" s="45">
         <f>'DCF'!J29</f>
         <v/>
       </c>
-      <c r="K57" s="45">
+      <c r="K58" s="45">
         <f>'DCF'!K29</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="41" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="41" t="inlineStr">
         <is>
           <t>Levered free cash flow</t>
         </is>
       </c>
-      <c r="G58" s="51">
-        <f>G55+G46-G56-G57</f>
-        <v/>
-      </c>
-      <c r="H58" s="51">
-        <f>H55+H46-H56-H57</f>
-        <v/>
-      </c>
-      <c r="I58" s="51">
-        <f>I55+I46-I56-I57</f>
-        <v/>
-      </c>
-      <c r="J58" s="51">
-        <f>J55+J46-J56-J57</f>
-        <v/>
-      </c>
-      <c r="K58" s="51">
-        <f>K55+K46-K56-K57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="23" t="inlineStr">
+      <c r="G59" s="51">
+        <f>G56+G47-G57-G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="51">
+        <f>H56+H47-H57-H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="51">
+        <f>I56+I47-I57-I58</f>
+        <v/>
+      </c>
+      <c r="J59" s="51">
+        <f>J56+J47-J57-J58</f>
+        <v/>
+      </c>
+      <c r="K59" s="51">
+        <f>K56+K47-K57-K58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="23" t="inlineStr">
         <is>
           <t>Cash sweep</t>
         </is>
       </c>
-      <c r="C60" s="23" t="n"/>
-      <c r="D60" s="23" t="n"/>
-      <c r="E60" s="23" t="n"/>
-      <c r="F60" s="23" t="n"/>
-      <c r="G60" s="23" t="n"/>
-      <c r="H60" s="23" t="n"/>
-      <c r="I60" s="23" t="n"/>
-      <c r="J60" s="23" t="n"/>
-      <c r="K60" s="23" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="G61" s="50">
-        <f>$D$22</f>
-        <v/>
-      </c>
-      <c r="H61" s="50">
-        <f>G66</f>
-        <v/>
-      </c>
-      <c r="I61" s="50">
-        <f>H66</f>
-        <v/>
-      </c>
-      <c r="J61" s="50">
-        <f>I66</f>
-        <v/>
-      </c>
-      <c r="K61" s="50">
-        <f>J66</f>
-        <v/>
-      </c>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="23" t="n"/>
+      <c r="F61" s="23" t="n"/>
+      <c r="G61" s="23" t="n"/>
+      <c r="H61" s="23" t="n"/>
+      <c r="I61" s="23" t="n"/>
+      <c r="J61" s="23" t="n"/>
+      <c r="K61" s="23" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>Less: mandatory amortization</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="G62" s="50">
-        <f>G70+G76</f>
+        <f>$D$23</f>
         <v/>
       </c>
       <c r="H62" s="50">
-        <f>H70+H76</f>
+        <f>G67</f>
         <v/>
       </c>
       <c r="I62" s="50">
-        <f>I70+I76</f>
+        <f>H67</f>
         <v/>
       </c>
       <c r="J62" s="50">
-        <f>J70+J76</f>
+        <f>I67</f>
         <v/>
       </c>
       <c r="K62" s="50">
-        <f>K70+K76</f>
+        <f>J67</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>Cash available after minimum cash</t>
+          <t>Less: mandatory amortization</t>
         </is>
       </c>
       <c r="G63" s="50">
-        <f>G61+G58-G62-$D$20</f>
+        <f>G71+G77</f>
         <v/>
       </c>
       <c r="H63" s="50">
-        <f>H61+H58-H62-$D$20</f>
+        <f>H71+H77</f>
         <v/>
       </c>
       <c r="I63" s="50">
-        <f>I61+I58-I62-$D$20</f>
+        <f>I71+I77</f>
         <v/>
       </c>
       <c r="J63" s="50">
-        <f>J61+J58-J62-$D$20</f>
+        <f>J71+J77</f>
         <v/>
       </c>
       <c r="K63" s="50">
-        <f>K61+K58-K62-$D$20</f>
+        <f>K71+K77</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>Cash swept to optional prepayment</t>
-        </is>
-      </c>
-      <c r="G64" s="45">
-        <f>MAX(G63,0)*'Inputs'!$D$54</f>
-        <v/>
-      </c>
-      <c r="H64" s="45">
-        <f>MAX(H63,0)*'Inputs'!$D$54</f>
-        <v/>
-      </c>
-      <c r="I64" s="45">
-        <f>MAX(I63,0)*'Inputs'!$D$54</f>
-        <v/>
-      </c>
-      <c r="J64" s="45">
-        <f>MAX(J63,0)*'Inputs'!$D$54</f>
-        <v/>
-      </c>
-      <c r="K64" s="45">
-        <f>MAX(K63,0)*'Inputs'!$D$54</f>
+          <t>Cash available after minimum cash</t>
+        </is>
+      </c>
+      <c r="G64" s="50">
+        <f>G62+G59-G63-$D$21</f>
+        <v/>
+      </c>
+      <c r="H64" s="50">
+        <f>H62+H59-H63-$D$21</f>
+        <v/>
+      </c>
+      <c r="I64" s="50">
+        <f>I62+I59-I63-$D$21</f>
+        <v/>
+      </c>
+      <c r="J64" s="50">
+        <f>J62+J59-J63-$D$21</f>
+        <v/>
+      </c>
+      <c r="K64" s="50">
+        <f>K62+K59-K63-$D$21</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="24" t="inlineStr">
         <is>
+          <t>Cash swept to optional prepayment</t>
+        </is>
+      </c>
+      <c r="G65" s="45">
+        <f>MAX(G64,0)*'Inputs'!$D$55</f>
+        <v/>
+      </c>
+      <c r="H65" s="45">
+        <f>MAX(H64,0)*'Inputs'!$D$55</f>
+        <v/>
+      </c>
+      <c r="I65" s="45">
+        <f>MAX(I64,0)*'Inputs'!$D$55</f>
+        <v/>
+      </c>
+      <c r="J65" s="45">
+        <f>MAX(J64,0)*'Inputs'!$D$55</f>
+        <v/>
+      </c>
+      <c r="K65" s="45">
+        <f>MAX(K64,0)*'Inputs'!$D$55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="24" t="inlineStr">
+        <is>
           <t>Optional prepayments</t>
         </is>
       </c>
-      <c r="G65" s="50">
-        <f>G71+G77</f>
-        <v/>
-      </c>
-      <c r="H65" s="50">
-        <f>H71+H77</f>
-        <v/>
-      </c>
-      <c r="I65" s="50">
-        <f>I71+I77</f>
-        <v/>
-      </c>
-      <c r="J65" s="50">
-        <f>J71+J77</f>
-        <v/>
-      </c>
-      <c r="K65" s="50">
-        <f>K71+K77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="41" t="inlineStr">
+      <c r="G66" s="50">
+        <f>G72+G78</f>
+        <v/>
+      </c>
+      <c r="H66" s="50">
+        <f>H72+H78</f>
+        <v/>
+      </c>
+      <c r="I66" s="50">
+        <f>I72+I78</f>
+        <v/>
+      </c>
+      <c r="J66" s="50">
+        <f>J72+J78</f>
+        <v/>
+      </c>
+      <c r="K66" s="50">
+        <f>K72+K78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>Cash, end of year</t>
         </is>
       </c>
-      <c r="G66" s="51">
-        <f>G61+G58-G62-G65</f>
-        <v/>
-      </c>
-      <c r="H66" s="51">
-        <f>H61+H58-H62-H65</f>
-        <v/>
-      </c>
-      <c r="I66" s="51">
-        <f>I61+I58-I62-I65</f>
-        <v/>
-      </c>
-      <c r="J66" s="51">
-        <f>J61+J58-J62-J65</f>
-        <v/>
-      </c>
-      <c r="K66" s="51">
-        <f>K61+K58-K62-K65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="23" t="inlineStr">
+      <c r="G67" s="51">
+        <f>G62+G59-G63-G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="51">
+        <f>H62+H59-H63-H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="51">
+        <f>I62+I59-I63-I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="51">
+        <f>J62+J59-J63-J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="51">
+        <f>K62+K59-K63-K66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="23" t="inlineStr">
         <is>
           <t>Senior Term Loan B (5.50%, priority 1)</t>
         </is>
       </c>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="23" t="n"/>
-      <c r="E68" s="23" t="n"/>
-      <c r="F68" s="23" t="n"/>
-      <c r="G68" s="23" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="23" t="n"/>
-      <c r="K68" s="23" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="G69" s="50">
-        <f>$D$36</f>
-        <v/>
-      </c>
-      <c r="H69" s="50">
-        <f>G72</f>
-        <v/>
-      </c>
-      <c r="I69" s="50">
-        <f>H72</f>
-        <v/>
-      </c>
-      <c r="J69" s="50">
-        <f>I72</f>
-        <v/>
-      </c>
-      <c r="K69" s="50">
-        <f>J72</f>
-        <v/>
-      </c>
+      <c r="C69" s="23" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+      <c r="F69" s="23" t="n"/>
+      <c r="G69" s="23" t="n"/>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="23" t="n"/>
+      <c r="J69" s="23" t="n"/>
+      <c r="K69" s="23" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>Mandatory amortization</t>
-        </is>
-      </c>
-      <c r="G70" s="45">
-        <f>MIN(G69,$D$36*'Inputs'!$D$65)</f>
-        <v/>
-      </c>
-      <c r="H70" s="45">
-        <f>MIN(H69,$D$36*'Inputs'!$D$65)</f>
-        <v/>
-      </c>
-      <c r="I70" s="45">
-        <f>MIN(I69,$D$36*'Inputs'!$D$65)</f>
-        <v/>
-      </c>
-      <c r="J70" s="45">
-        <f>MIN(J69,$D$36*'Inputs'!$D$65)</f>
-        <v/>
-      </c>
-      <c r="K70" s="45">
-        <f>MIN(K69,$D$36*'Inputs'!$D$65)</f>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="G70" s="50">
+        <f>$D$37</f>
+        <v/>
+      </c>
+      <c r="H70" s="50">
+        <f>G73</f>
+        <v/>
+      </c>
+      <c r="I70" s="50">
+        <f>H73</f>
+        <v/>
+      </c>
+      <c r="J70" s="50">
+        <f>I73</f>
+        <v/>
+      </c>
+      <c r="K70" s="50">
+        <f>J73</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="24" t="inlineStr">
         <is>
+          <t>Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="G71" s="45">
+        <f>MIN(G70,$D$37*'Inputs'!$D$66)</f>
+        <v/>
+      </c>
+      <c r="H71" s="45">
+        <f>MIN(H70,$D$37*'Inputs'!$D$66)</f>
+        <v/>
+      </c>
+      <c r="I71" s="45">
+        <f>MIN(I70,$D$37*'Inputs'!$D$66)</f>
+        <v/>
+      </c>
+      <c r="J71" s="45">
+        <f>MIN(J70,$D$37*'Inputs'!$D$66)</f>
+        <v/>
+      </c>
+      <c r="K71" s="45">
+        <f>MIN(K70,$D$37*'Inputs'!$D$66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="24" t="inlineStr">
+        <is>
           <t>Optional prepayment (sweep)</t>
         </is>
       </c>
-      <c r="G71" s="45">
-        <f>IF('Inputs'!$D$66=1,MIN(G64,G69-G70),0)</f>
-        <v/>
-      </c>
-      <c r="H71" s="45">
-        <f>IF('Inputs'!$D$66=1,MIN(H64,H69-H70),0)</f>
-        <v/>
-      </c>
-      <c r="I71" s="45">
-        <f>IF('Inputs'!$D$66=1,MIN(I64,I69-I70),0)</f>
-        <v/>
-      </c>
-      <c r="J71" s="45">
-        <f>IF('Inputs'!$D$66=1,MIN(J64,J69-J70),0)</f>
-        <v/>
-      </c>
-      <c r="K71" s="45">
-        <f>IF('Inputs'!$D$66=1,MIN(K64,K69-K70),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="41" t="inlineStr">
+      <c r="G72" s="45">
+        <f>IF('Inputs'!$D$67=1,MIN(G65,G70-G71),0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="45">
+        <f>IF('Inputs'!$D$67=1,MIN(H65,H70-H71),0)</f>
+        <v/>
+      </c>
+      <c r="I72" s="45">
+        <f>IF('Inputs'!$D$67=1,MIN(I65,I70-I71),0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="45">
+        <f>IF('Inputs'!$D$67=1,MIN(J65,J70-J71),0)</f>
+        <v/>
+      </c>
+      <c r="K72" s="45">
+        <f>IF('Inputs'!$D$67=1,MIN(K65,K70-K71),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="41" t="inlineStr">
         <is>
           <t>Ending balance</t>
         </is>
       </c>
-      <c r="G72" s="46">
-        <f>G69-G70-G71</f>
-        <v/>
-      </c>
-      <c r="H72" s="46">
-        <f>H69-H70-H71</f>
-        <v/>
-      </c>
-      <c r="I72" s="46">
-        <f>I69-I70-I71</f>
-        <v/>
-      </c>
-      <c r="J72" s="46">
-        <f>J69-J70-J71</f>
-        <v/>
-      </c>
-      <c r="K72" s="46">
-        <f>K69-K70-K71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="23" t="inlineStr">
+      <c r="G73" s="46">
+        <f>G70-G71-G72</f>
+        <v/>
+      </c>
+      <c r="H73" s="46">
+        <f>H70-H71-H72</f>
+        <v/>
+      </c>
+      <c r="I73" s="46">
+        <f>I70-I71-I72</f>
+        <v/>
+      </c>
+      <c r="J73" s="46">
+        <f>J70-J71-J72</f>
+        <v/>
+      </c>
+      <c r="K73" s="46">
+        <f>K70-K71-K72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="23" t="inlineStr">
         <is>
           <t>Senior Subordinated Notes (8.00%, priority 2)</t>
         </is>
       </c>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-      <c r="F74" s="23" t="n"/>
-      <c r="G74" s="23" t="n"/>
-      <c r="H74" s="23" t="n"/>
-      <c r="I74" s="23" t="n"/>
-      <c r="J74" s="23" t="n"/>
-      <c r="K74" s="23" t="n"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="G75" s="50">
-        <f>$D$37</f>
-        <v/>
-      </c>
-      <c r="H75" s="50">
-        <f>G78</f>
-        <v/>
-      </c>
-      <c r="I75" s="50">
-        <f>H78</f>
-        <v/>
-      </c>
-      <c r="J75" s="50">
-        <f>I78</f>
-        <v/>
-      </c>
-      <c r="K75" s="50">
-        <f>J78</f>
-        <v/>
-      </c>
+      <c r="C75" s="23" t="n"/>
+      <c r="D75" s="23" t="n"/>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="23" t="n"/>
+      <c r="G75" s="23" t="n"/>
+      <c r="H75" s="23" t="n"/>
+      <c r="I75" s="23" t="n"/>
+      <c r="J75" s="23" t="n"/>
+      <c r="K75" s="23" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>Mandatory amortization</t>
-        </is>
-      </c>
-      <c r="G76" s="45">
-        <f>MIN(G75,$D$37*'Inputs'!$D$71)</f>
-        <v/>
-      </c>
-      <c r="H76" s="45">
-        <f>MIN(H75,$D$37*'Inputs'!$D$71)</f>
-        <v/>
-      </c>
-      <c r="I76" s="45">
-        <f>MIN(I75,$D$37*'Inputs'!$D$71)</f>
-        <v/>
-      </c>
-      <c r="J76" s="45">
-        <f>MIN(J75,$D$37*'Inputs'!$D$71)</f>
-        <v/>
-      </c>
-      <c r="K76" s="45">
-        <f>MIN(K75,$D$37*'Inputs'!$D$71)</f>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="G76" s="50">
+        <f>$D$38</f>
+        <v/>
+      </c>
+      <c r="H76" s="50">
+        <f>G79</f>
+        <v/>
+      </c>
+      <c r="I76" s="50">
+        <f>H79</f>
+        <v/>
+      </c>
+      <c r="J76" s="50">
+        <f>I79</f>
+        <v/>
+      </c>
+      <c r="K76" s="50">
+        <f>J79</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="24" t="inlineStr">
         <is>
+          <t>Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="G77" s="45">
+        <f>MIN(G76,$D$38*'Inputs'!$D$72)</f>
+        <v/>
+      </c>
+      <c r="H77" s="45">
+        <f>MIN(H76,$D$38*'Inputs'!$D$72)</f>
+        <v/>
+      </c>
+      <c r="I77" s="45">
+        <f>MIN(I76,$D$38*'Inputs'!$D$72)</f>
+        <v/>
+      </c>
+      <c r="J77" s="45">
+        <f>MIN(J76,$D$38*'Inputs'!$D$72)</f>
+        <v/>
+      </c>
+      <c r="K77" s="45">
+        <f>MIN(K76,$D$38*'Inputs'!$D$72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="24" t="inlineStr">
+        <is>
           <t>Optional prepayment (sweep)</t>
         </is>
       </c>
-      <c r="G77" s="45">
-        <f>IF('Inputs'!$D$72=1,MIN(G64-G71,G75-G76),0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="45">
-        <f>IF('Inputs'!$D$72=1,MIN(H64-H71,H75-H76),0)</f>
-        <v/>
-      </c>
-      <c r="I77" s="45">
-        <f>IF('Inputs'!$D$72=1,MIN(I64-I71,I75-I76),0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="45">
-        <f>IF('Inputs'!$D$72=1,MIN(J64-J71,J75-J76),0)</f>
-        <v/>
-      </c>
-      <c r="K77" s="45">
-        <f>IF('Inputs'!$D$72=1,MIN(K64-K71,K75-K76),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="41" t="inlineStr">
+      <c r="G78" s="45">
+        <f>IF('Inputs'!$D$73=1,MIN(G65-G72,G76-G77),0)</f>
+        <v/>
+      </c>
+      <c r="H78" s="45">
+        <f>IF('Inputs'!$D$73=1,MIN(H65-H72,H76-H77),0)</f>
+        <v/>
+      </c>
+      <c r="I78" s="45">
+        <f>IF('Inputs'!$D$73=1,MIN(I65-I72,I76-I77),0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="45">
+        <f>IF('Inputs'!$D$73=1,MIN(J65-J72,J76-J77),0)</f>
+        <v/>
+      </c>
+      <c r="K78" s="45">
+        <f>IF('Inputs'!$D$73=1,MIN(K65-K72,K76-K77),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="41" t="inlineStr">
         <is>
           <t>Ending balance</t>
         </is>
       </c>
-      <c r="G78" s="46">
-        <f>G75-G76-G77</f>
-        <v/>
-      </c>
-      <c r="H78" s="46">
-        <f>H75-H76-H77</f>
-        <v/>
-      </c>
-      <c r="I78" s="46">
-        <f>I75-I76-I77</f>
-        <v/>
-      </c>
-      <c r="J78" s="46">
-        <f>J75-J76-J77</f>
-        <v/>
-      </c>
-      <c r="K78" s="46">
-        <f>K75-K76-K77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="23" t="inlineStr">
+      <c r="G79" s="46">
+        <f>G76-G77-G78</f>
+        <v/>
+      </c>
+      <c r="H79" s="46">
+        <f>H76-H77-H78</f>
+        <v/>
+      </c>
+      <c r="I79" s="46">
+        <f>I76-I77-I78</f>
+        <v/>
+      </c>
+      <c r="J79" s="46">
+        <f>J76-J77-J78</f>
+        <v/>
+      </c>
+      <c r="K79" s="46">
+        <f>K76-K77-K78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="23" t="inlineStr">
         <is>
           <t>Credit statistics &amp; covenants</t>
         </is>
       </c>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="n"/>
-      <c r="F80" s="23" t="n"/>
-      <c r="G80" s="23" t="n"/>
-      <c r="H80" s="23" t="n"/>
-      <c r="I80" s="23" t="n"/>
-      <c r="J80" s="23" t="n"/>
-      <c r="K80" s="23" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="41" t="inlineStr">
+      <c r="C81" s="23" t="n"/>
+      <c r="D81" s="23" t="n"/>
+      <c r="E81" s="23" t="n"/>
+      <c r="F81" s="23" t="n"/>
+      <c r="G81" s="23" t="n"/>
+      <c r="H81" s="23" t="n"/>
+      <c r="I81" s="23" t="n"/>
+      <c r="J81" s="23" t="n"/>
+      <c r="K81" s="23" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="41" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="G81" s="46">
-        <f>G72+G78</f>
-        <v/>
-      </c>
-      <c r="H81" s="46">
-        <f>H72+H78</f>
-        <v/>
-      </c>
-      <c r="I81" s="46">
-        <f>I72+I78</f>
-        <v/>
-      </c>
-      <c r="J81" s="46">
-        <f>J72+J78</f>
-        <v/>
-      </c>
-      <c r="K81" s="46">
-        <f>K72+K78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>Net debt</t>
-        </is>
-      </c>
-      <c r="G82" s="50">
-        <f>G81-G66</f>
-        <v/>
-      </c>
-      <c r="H82" s="50">
-        <f>H81-H66</f>
-        <v/>
-      </c>
-      <c r="I82" s="50">
-        <f>I81-I66</f>
-        <v/>
-      </c>
-      <c r="J82" s="50">
-        <f>J81-J66</f>
-        <v/>
-      </c>
-      <c r="K82" s="50">
-        <f>K81-K66</f>
+      <c r="G82" s="46">
+        <f>G73+G79</f>
+        <v/>
+      </c>
+      <c r="H82" s="46">
+        <f>H73+H79</f>
+        <v/>
+      </c>
+      <c r="I82" s="46">
+        <f>I73+I79</f>
+        <v/>
+      </c>
+      <c r="J82" s="46">
+        <f>J73+J79</f>
+        <v/>
+      </c>
+      <c r="K82" s="46">
+        <f>K73+K79</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>Total debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="G83" s="69">
-        <f>G81/G45</f>
-        <v/>
-      </c>
-      <c r="H83" s="69">
-        <f>H81/H45</f>
-        <v/>
-      </c>
-      <c r="I83" s="69">
-        <f>I81/I45</f>
-        <v/>
-      </c>
-      <c r="J83" s="69">
-        <f>J81/J45</f>
-        <v/>
-      </c>
-      <c r="K83" s="69">
-        <f>K81/K45</f>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="G83" s="50">
+        <f>G82-G67</f>
+        <v/>
+      </c>
+      <c r="H83" s="50">
+        <f>H82-H67</f>
+        <v/>
+      </c>
+      <c r="I83" s="50">
+        <f>I82-I67</f>
+        <v/>
+      </c>
+      <c r="J83" s="50">
+        <f>J82-J67</f>
+        <v/>
+      </c>
+      <c r="K83" s="50">
+        <f>K82-K67</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>EBITDA / interest expense</t>
+          <t>Total debt / EBITDA</t>
         </is>
       </c>
       <c r="G84" s="69">
-        <f>IF(G51=0,"n.m.",G45/G51)</f>
+        <f>G82/G46</f>
         <v/>
       </c>
       <c r="H84" s="69">
-        <f>IF(H51=0,"n.m.",H45/H51)</f>
+        <f>H82/H46</f>
         <v/>
       </c>
       <c r="I84" s="69">
-        <f>IF(I51=0,"n.m.",I45/I51)</f>
+        <f>I82/I46</f>
         <v/>
       </c>
       <c r="J84" s="69">
-        <f>IF(J51=0,"n.m.",J45/J51)</f>
+        <f>J82/J46</f>
         <v/>
       </c>
       <c r="K84" s="69">
-        <f>IF(K51=0,"n.m.",K45/K51)</f>
+        <f>K82/K46</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>Covenant: max leverage</t>
-        </is>
-      </c>
-      <c r="G85" s="67">
-        <f>'Inputs'!$D$59</f>
-        <v/>
-      </c>
-      <c r="H85" s="67">
-        <f>'Inputs'!$D$59</f>
-        <v/>
-      </c>
-      <c r="I85" s="67">
-        <f>'Inputs'!$D$59</f>
-        <v/>
-      </c>
-      <c r="J85" s="67">
-        <f>'Inputs'!$D$59</f>
-        <v/>
-      </c>
-      <c r="K85" s="67">
-        <f>'Inputs'!$D$59</f>
+          <t>EBITDA / interest expense</t>
+        </is>
+      </c>
+      <c r="G85" s="69">
+        <f>IF(G52=0,"n.m.",G46/G52)</f>
+        <v/>
+      </c>
+      <c r="H85" s="69">
+        <f>IF(H52=0,"n.m.",H46/H52)</f>
+        <v/>
+      </c>
+      <c r="I85" s="69">
+        <f>IF(I52=0,"n.m.",I46/I52)</f>
+        <v/>
+      </c>
+      <c r="J85" s="69">
+        <f>IF(J52=0,"n.m.",J46/J52)</f>
+        <v/>
+      </c>
+      <c r="K85" s="69">
+        <f>IF(K52=0,"n.m.",K46/K52)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>EBITDA cushion to leverage covenant</t>
-        </is>
-      </c>
-      <c r="G86" s="31">
-        <f>1-(G81/G85)/G45</f>
-        <v/>
-      </c>
-      <c r="H86" s="31">
-        <f>1-(H81/H85)/H45</f>
-        <v/>
-      </c>
-      <c r="I86" s="31">
-        <f>1-(I81/I85)/I45</f>
-        <v/>
-      </c>
-      <c r="J86" s="31">
-        <f>1-(J81/J85)/J45</f>
-        <v/>
-      </c>
-      <c r="K86" s="31">
-        <f>1-(K81/K85)/K45</f>
+          <t>Covenant: max leverage</t>
+        </is>
+      </c>
+      <c r="G86" s="67">
+        <f>'Inputs'!$D$60</f>
+        <v/>
+      </c>
+      <c r="H86" s="67">
+        <f>'Inputs'!$D$60</f>
+        <v/>
+      </c>
+      <c r="I86" s="67">
+        <f>'Inputs'!$D$60</f>
+        <v/>
+      </c>
+      <c r="J86" s="67">
+        <f>'Inputs'!$D$60</f>
+        <v/>
+      </c>
+      <c r="K86" s="67">
+        <f>'Inputs'!$D$60</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>Covenant: min interest coverage</t>
-        </is>
-      </c>
-      <c r="G87" s="67">
-        <f>'Inputs'!$D$60</f>
-        <v/>
-      </c>
-      <c r="H87" s="67">
-        <f>'Inputs'!$D$60</f>
-        <v/>
-      </c>
-      <c r="I87" s="67">
-        <f>'Inputs'!$D$60</f>
-        <v/>
-      </c>
-      <c r="J87" s="67">
-        <f>'Inputs'!$D$60</f>
-        <v/>
-      </c>
-      <c r="K87" s="67">
-        <f>'Inputs'!$D$60</f>
+          <t>EBITDA cushion to leverage covenant</t>
+        </is>
+      </c>
+      <c r="G87" s="31">
+        <f>1-(G82/G86)/G46</f>
+        <v/>
+      </c>
+      <c r="H87" s="31">
+        <f>1-(H82/H86)/H46</f>
+        <v/>
+      </c>
+      <c r="I87" s="31">
+        <f>1-(I82/I86)/I46</f>
+        <v/>
+      </c>
+      <c r="J87" s="31">
+        <f>1-(J82/J86)/J46</f>
+        <v/>
+      </c>
+      <c r="K87" s="31">
+        <f>1-(K82/K86)/K46</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>EBITDA cushion to coverage covenant</t>
-        </is>
-      </c>
-      <c r="G88" s="31">
-        <f>1-G87*G51/G45</f>
-        <v/>
-      </c>
-      <c r="H88" s="31">
-        <f>1-H87*H51/H45</f>
-        <v/>
-      </c>
-      <c r="I88" s="31">
-        <f>1-I87*I51/I45</f>
-        <v/>
-      </c>
-      <c r="J88" s="31">
-        <f>1-J87*J51/J45</f>
-        <v/>
-      </c>
-      <c r="K88" s="31">
-        <f>1-K87*K51/K45</f>
+          <t>Covenant: min interest coverage</t>
+        </is>
+      </c>
+      <c r="G88" s="67">
+        <f>'Inputs'!$D$61</f>
+        <v/>
+      </c>
+      <c r="H88" s="67">
+        <f>'Inputs'!$D$61</f>
+        <v/>
+      </c>
+      <c r="I88" s="67">
+        <f>'Inputs'!$D$61</f>
+        <v/>
+      </c>
+      <c r="J88" s="67">
+        <f>'Inputs'!$D$61</f>
+        <v/>
+      </c>
+      <c r="K88" s="67">
+        <f>'Inputs'!$D$61</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="24" t="inlineStr">
         <is>
+          <t>EBITDA cushion to coverage covenant</t>
+        </is>
+      </c>
+      <c r="G89" s="31">
+        <f>1-G88*G52/G46</f>
+        <v/>
+      </c>
+      <c r="H89" s="31">
+        <f>1-H88*H52/H46</f>
+        <v/>
+      </c>
+      <c r="I89" s="31">
+        <f>1-I88*I52/I46</f>
+        <v/>
+      </c>
+      <c r="J89" s="31">
+        <f>1-J88*J52/J46</f>
+        <v/>
+      </c>
+      <c r="K89" s="31">
+        <f>1-K88*K52/K46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="24" t="inlineStr">
+        <is>
           <t>Covenant compliance</t>
         </is>
       </c>
-      <c r="G89" s="70">
-        <f>IF(AND(G83&lt;=G85,G88&gt;=0),"Pass","BREACH")</f>
-        <v/>
-      </c>
-      <c r="H89" s="70">
-        <f>IF(AND(H83&lt;=H85,H88&gt;=0),"Pass","BREACH")</f>
-        <v/>
-      </c>
-      <c r="I89" s="70">
-        <f>IF(AND(I83&lt;=I85,I88&gt;=0),"Pass","BREACH")</f>
-        <v/>
-      </c>
-      <c r="J89" s="70">
-        <f>IF(AND(J83&lt;=J85,J88&gt;=0),"Pass","BREACH")</f>
-        <v/>
-      </c>
-      <c r="K89" s="70">
-        <f>IF(AND(K83&lt;=K85,K88&gt;=0),"Pass","BREACH")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="23" t="inlineStr">
+      <c r="G90" s="70">
+        <f>IF(AND(G84&lt;=G86,G89&gt;=0),"Pass","BREACH")</f>
+        <v/>
+      </c>
+      <c r="H90" s="70">
+        <f>IF(AND(H84&lt;=H86,H89&gt;=0),"Pass","BREACH")</f>
+        <v/>
+      </c>
+      <c r="I90" s="70">
+        <f>IF(AND(I84&lt;=I86,I89&gt;=0),"Pass","BREACH")</f>
+        <v/>
+      </c>
+      <c r="J90" s="70">
+        <f>IF(AND(J84&lt;=J86,J89&gt;=0),"Pass","BREACH")</f>
+        <v/>
+      </c>
+      <c r="K90" s="70">
+        <f>IF(AND(K84&lt;=K86,K89&gt;=0),"Pass","BREACH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="23" t="inlineStr">
         <is>
           <t>Exit &amp; sponsor returns</t>
         </is>
       </c>
-      <c r="C91" s="23" t="n"/>
-      <c r="D91" s="23" t="n"/>
-      <c r="E91" s="23" t="n"/>
-      <c r="F91" s="23" t="n"/>
-      <c r="G91" s="23" t="n"/>
-      <c r="H91" s="23" t="n"/>
-      <c r="I91" s="23" t="n"/>
-      <c r="J91" s="23" t="n"/>
-      <c r="K91" s="23" t="n"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>Exit-year EBITDA (FY2020)</t>
-        </is>
-      </c>
-      <c r="D92" s="50">
-        <f>K45</f>
-        <v/>
-      </c>
+      <c r="C92" s="23" t="n"/>
+      <c r="D92" s="23" t="n"/>
+      <c r="E92" s="23" t="n"/>
+      <c r="F92" s="23" t="n"/>
+      <c r="G92" s="23" t="n"/>
+      <c r="H92" s="23" t="n"/>
+      <c r="I92" s="23" t="n"/>
+      <c r="J92" s="23" t="n"/>
+      <c r="K92" s="23" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="24" t="inlineStr">
         <is>
+          <t>Exit-year EBITDA (FY2020)</t>
+        </is>
+      </c>
+      <c r="D93" s="50">
+        <f>K46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="24" t="inlineStr">
+        <is>
           <t>Exit EV / EBITDA</t>
         </is>
       </c>
-      <c r="D93" s="67">
-        <f>'Inputs'!$D$51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="41" t="inlineStr">
+      <c r="D94" s="67">
+        <f>'Inputs'!$D$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="41" t="inlineStr">
         <is>
           <t>Exit enterprise value</t>
         </is>
       </c>
-      <c r="D94" s="46">
-        <f>$D$92*$D$93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="24" t="inlineStr">
-        <is>
-          <t>Less: debt outstanding</t>
-        </is>
-      </c>
-      <c r="D95" s="50">
-        <f>K81</f>
+      <c r="D95" s="46">
+        <f>$D$93*$D$94</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>Plus: cash</t>
+          <t>Less: debt outstanding</t>
         </is>
       </c>
       <c r="D96" s="50">
-        <f>K66</f>
+        <f>K82</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="24" t="inlineStr">
         <is>
+          <t>Plus: cash</t>
+        </is>
+      </c>
+      <c r="D97" s="50">
+        <f>K67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="24" t="inlineStr">
+        <is>
           <t>Plus: trapped offshore cash, after repatriation tax</t>
         </is>
       </c>
-      <c r="D97" s="45">
-        <f>$D$25*(1-'Inputs'!$D$16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="41" t="inlineStr">
-        <is>
-          <t>Exit equity value</t>
-        </is>
-      </c>
-      <c r="D98" s="51">
-        <f>$D$94-$D$95+$D$96+$D$97</f>
+      <c r="D98" s="45">
+        <f>$D$26*(1-'Inputs'!$D$16)</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="41" t="inlineStr">
-        <is>
-          <t>Sponsor cash flows</t>
-        </is>
-      </c>
-      <c r="F99" s="46">
-        <f>-$D$39</f>
-        <v/>
-      </c>
-      <c r="G99" s="46">
-        <f>IF(G$4=K$4,$D$98,0)</f>
-        <v/>
-      </c>
-      <c r="H99" s="46">
-        <f>IF(H$4=K$4,$D$98,0)</f>
-        <v/>
-      </c>
-      <c r="I99" s="46">
-        <f>IF(I$4=K$4,$D$98,0)</f>
-        <v/>
-      </c>
-      <c r="J99" s="46">
-        <f>IF(J$4=K$4,$D$98,0)</f>
-        <v/>
-      </c>
-      <c r="K99" s="46">
-        <f>IF(K$4=K$4,$D$98,0)</f>
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>Less: noncontrolling interests</t>
+        </is>
+      </c>
+      <c r="D99" s="50">
+        <f>$D$11</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="41" t="inlineStr">
         <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="D100" s="71">
-        <f>$D$98/$D$39</f>
+          <t>Exit equity value</t>
+        </is>
+      </c>
+      <c r="D100" s="51">
+        <f>$D$95-$D$96+$D$97+$D$98-$D$99</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="41" t="inlineStr">
         <is>
+          <t>Sponsor cash flows</t>
+        </is>
+      </c>
+      <c r="F101" s="46">
+        <f>-$D$40</f>
+        <v/>
+      </c>
+      <c r="G101" s="46">
+        <f>IF(G$4=K$4,$D$100,0)</f>
+        <v/>
+      </c>
+      <c r="H101" s="46">
+        <f>IF(H$4=K$4,$D$100,0)</f>
+        <v/>
+      </c>
+      <c r="I101" s="46">
+        <f>IF(I$4=K$4,$D$100,0)</f>
+        <v/>
+      </c>
+      <c r="J101" s="46">
+        <f>IF(J$4=K$4,$D$100,0)</f>
+        <v/>
+      </c>
+      <c r="K101" s="46">
+        <f>IF(K$4=K$4,$D$100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="41" t="inlineStr">
+        <is>
+          <t>MOIC</t>
+        </is>
+      </c>
+      <c r="D102" s="71">
+        <f>$D$100/$D$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="41" t="inlineStr">
+        <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="D101" s="72">
-        <f>IRR(F99:K99)</f>
+      <c r="D103" s="72">
+        <f>IRR(F101:K101)</f>
         <v/>
       </c>
     </row>
@@ -10551,23 +10832,23 @@
         <v/>
       </c>
       <c r="D12" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C12-D$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C12-D$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E12" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C12-E$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C12-E$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F12" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C12-F$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C12-F$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G12" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C12-G$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C12-G$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H12" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C12-H$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C12)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C12-H$11)/(1+$C12)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10577,23 +10858,23 @@
         <v/>
       </c>
       <c r="D13" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C13-D$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C13-D$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E13" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C13-E$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C13-E$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F13" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C13-F$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C13-F$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G13" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C13-G$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C13-G$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H13" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C13-H$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C13)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C13-H$11)/(1+$C13)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10603,23 +10884,23 @@
         <v/>
       </c>
       <c r="D14" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C14-D$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C14-D$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E14" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C14-E$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C14-E$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F14" s="75">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C14-F$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C14-F$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G14" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C14-G$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C14-G$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H14" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C14-H$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C14)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C14-H$11)/(1+$C14)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10629,23 +10910,23 @@
         <v/>
       </c>
       <c r="D15" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C15-D$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C15-D$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E15" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C15-E$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C15-E$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F15" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C15-F$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C15-F$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G15" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C15-G$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C15-G$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H15" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C15-H$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C15)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C15-H$11)/(1+$C15)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10655,23 +10936,23 @@
         <v/>
       </c>
       <c r="D16" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C16-D$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+D$11)/($C16-D$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E16" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C16-E$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+E$11)/($C16-E$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F16" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C16-F$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+F$11)/($C16-F$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G16" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C16-G$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+G$11)/($C16-G$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H16" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C16-H$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+$C16)^(-'DCF'!$G$32:$K$32))+'DCF'!$K$30*(1+H$11)/($C16-H$11)/(1+$C16)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10728,23 +11009,23 @@
         <v/>
       </c>
       <c r="D21" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C21/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C21/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E21" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C21/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C21/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F21" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C21/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C21/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G21" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C21/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C21/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H21" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C21/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C21/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10754,23 +11035,23 @@
         <v/>
       </c>
       <c r="D22" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C22/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C22/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E22" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C22/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C22/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F22" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C22/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C22/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G22" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C22/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C22/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H22" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C22/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C22/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10780,23 +11061,23 @@
         <v/>
       </c>
       <c r="D23" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C23/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C23/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E23" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C23/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C23/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C23/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C23/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G23" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C23/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C23/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H23" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C23/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C23/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10806,23 +11087,23 @@
         <v/>
       </c>
       <c r="D24" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C24/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C24/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E24" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C24/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C24/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F24" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C24/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C24/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G24" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C24/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C24/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H24" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C24/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C24/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
@@ -10832,23 +11113,23 @@
         <v/>
       </c>
       <c r="D25" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C25/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+D$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C25/(1+D$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="E25" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C25/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+E$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C25/(1+E$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="F25" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C25/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+F$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C25/(1+F$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="G25" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C25/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+G$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C25/(1+G$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
       <c r="H25" s="54">
-        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$17*$C25/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46)/'DCF'!$D$48</f>
+        <f>(SUMPRODUCT('DCF'!$G$30:$K$30,(1+H$20)^(-'DCF'!$G$32:$K$32))+'IS'!$K$18*$C25/(1+H$20)^'DCF'!$K$31+'DCF'!$D$44+'DCF'!$D$45+'DCF'!$D$46+'DCF'!$D$47)/'DCF'!$D$49</f>
         <v/>
       </c>
     </row>
